--- a/docs/testing/EcoAlerta_Testware_Matriz_Casos_Ejecucion.xlsx
+++ b/docs/testing/EcoAlerta_Testware_Matriz_Casos_Ejecucion.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,6 +126,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -501,13 +502,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
@@ -524,7 +525,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Pilar (UNPilar) — Testing &amp; Calidad de Software 2026 — Mg. Pedro Brest | Estudiante / QA Lead: Raul Escobar</t>
+          <t>Universidad Nacional de Pilar (UNPilar) — Testing &amp; Calidad de Software 2026 — Mg. Pedro Brest | Período: 25/08/2026 al 02/11/2026</t>
         </is>
       </c>
     </row>
@@ -767,21 +768,119 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Gobernabilidad de Defectos y Asignación de Responsabilidades:</t>
+          <t>Equipo de Proyecto EcoAlerta (5 Integrantes) y Gobernabilidad:</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Responsabilidad Principal</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Escobar Raul</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Scrum Master</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Planificación, Cronograma PMBOK, Matriz RTM y Testware IEEE 829</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Kuhn Joaquin</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Diseñador UI/UX</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Prototipado, Interfaces, HomeScreen y Usabilidad ISO 25010</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Desarrollador FrontEnd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Pantallas React Native Expo, Auth Gate, Cámara y Fix BUG-101</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Benitez Angel</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Desarrollador BackEnd</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>API REST, Prisma ORM, PostgreSQL, Concurrencia y Fix BUG-102</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Benitez Facundo</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Analista de QA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Diseño y Ejecución de 57 Casos, Postman, Jest y Regresión</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>• Directiva de QA: El responsable de corregir cada defecto es unívocamente el mismo desarrollador que implementó el módulo o función.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Roles asignados: Dev Módulo 1 (Auth/RBAC), Dev Módulo 2A (Reportes), Dev Módulo 2B (Triaje/Agente), Dev Módulo 2C (Saneamiento), Dev Módulo 3A (Tienda), Dev Módulo 3B (Entrega), Dev Backend/BD, Dev Frontend UI.</t>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>• Trazabilidad de Bugs: BUG-101 asignado a Rodriguez Iván (FrontEnd) | BUG-102 asignado a Benitez Angel (BackEnd).</t>
         </is>
       </c>
     </row>
@@ -804,19 +903,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Tema</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Definición y Criterio Establecido</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Alcance de Pruebas</t>
         </is>
@@ -828,7 +927,7 @@
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Ambiente de Pruebas</t>
         </is>
@@ -840,7 +939,7 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Convención de Rutas API</t>
         </is>
@@ -852,7 +951,7 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Datos de Prueba Deterministas</t>
         </is>
@@ -864,7 +963,7 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Política de Corrección de Bugs</t>
         </is>
@@ -876,7 +975,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Gestión de Concurrencia</t>
         </is>
@@ -888,7 +987,7 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Política de Ecopuntos</t>
         </is>
@@ -900,7 +999,7 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Política de Expiración de Canjes</t>
         </is>
@@ -912,7 +1011,7 @@
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Protocolo de Inaccesibilidad</t>
         </is>
@@ -924,7 +1023,7 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Compresión Multimedia (RNF-02)</t>
         </is>
@@ -936,7 +1035,7 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Feedback Transaccional (RNF-10)</t>
         </is>
@@ -948,7 +1047,7 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Criterios de Aceptación BDD</t>
         </is>
@@ -960,7 +1059,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Estándar de Calidad ISO 25010</t>
         </is>
@@ -1001,91 +1100,91 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>ID del Caso</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Funcionalidad a testar</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Precondiciones</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Datos de prueba</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Pasos a ejecutar</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Resultado esperado</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Resultado Real</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Postcondiciones</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>Evidencia</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>ID Requerimiento</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>Herramienta</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="O1" s="8" t="inlineStr">
         <is>
           <t>Tipo de prueba</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="P1" s="8" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="Q1" s="8" t="inlineStr">
         <is>
           <t>Responsable Corrección Bug</t>
         </is>
@@ -1139,7 +1238,7 @@
           <t>HTTP 201 Created; token válido; rol CITIZEN asignado con 0 puntos</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -1176,7 +1275,7 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1326,7 @@
           <t>HTTP 409 Conflict recibido con mensaje exacto</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -1264,7 +1363,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1414,7 @@
           <t>Borde rojo renderizado; mensaje mostrado; no hubo petición HTTP</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -1352,7 +1451,7 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1502,7 @@
           <t>Validación cliente exitosa; texto exacto mostrado</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -1440,7 +1539,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1590,7 @@
           <t>Mensaje de error exacto mostrado</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -1528,7 +1627,7 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1678,7 @@
           <t>HTTP 200 OK; token emitido correctamente</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -1616,7 +1715,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1765,7 @@
           <t>HTTP 401 recibido y banner rojo desplegado</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -1703,7 +1802,7 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1853,7 @@
           <t>Navegación determinista según rol verificada</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -1791,7 +1890,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1941,7 @@
           <t>Sesión limpiada y redirección a Invitado verificada</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -1879,7 +1978,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -1930,7 +2029,7 @@
           <t>Renderizado en 185 ms; 3 tarjetas visibles</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -1967,7 +2066,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2117,7 @@
           <t>Texto verificado y navegación fluida</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -2055,7 +2154,7 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2205,7 @@
           <t>Catálogo explorable en modo lectura</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -2143,7 +2242,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2293,7 @@
           <t>Modal desplegado en 42 ms sin abrir hardware</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -2231,7 +2330,7 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2380,7 @@
           <t>Modal mostrado; carrito vacío</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -2318,7 +2417,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2467,7 @@
           <t>Acceso denegado con modal protegido</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -2405,7 +2504,7 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2555,7 @@
           <t>HTTP 201 Created; código emitido; estado PENDIENTE con 0 pts</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -2493,7 +2592,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2642,7 @@
           <t>Imagen reducida a 865 KB y 1080px (tras fix de algoritmo en BUG-101)</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -2580,7 +2679,7 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2729,7 @@
           <t>HTTP 400 Bad Request retornado con mensaje exacto</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -2667,7 +2766,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2816,7 @@
           <t>Campos verificados en BD</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -2754,7 +2853,7 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2903,7 @@
           <t>Archivado visual confirmado; registro físico preservado en BD</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -2841,7 +2940,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2990,7 @@
           <t>HTTP 200 OK; caso visible en bolsa</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -2928,7 +3027,7 @@
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -2978,7 +3077,7 @@
           <t>HTTP 200 OK; caso rechazado y cerrado con 0 pts</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3015,7 +3114,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3164,7 @@
           <t>HTTP 400 devuelto con bloqueo de validación</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3102,7 +3201,7 @@
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3251,7 @@
           <t>HTTP 400 recibido y banner 'Agente no disponible' mostrado</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3189,7 +3288,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3339,7 @@
           <t>Bolsa renderizada con semáforos correctos</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3277,7 +3376,7 @@
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3427,7 @@
           <t>Caso tomado con estado EN_VERIFICACION</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3365,7 +3464,7 @@
       </c>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3514,7 @@
           <t>1 asignación exitosa, 1 rechazo 409 controlado; cero condiciones de carrera</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3452,7 +3551,7 @@
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3601,7 @@
           <t>Bloqueo validado con mensaje de caso activo</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3539,7 +3638,7 @@
       </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3688,7 @@
           <t>Estado actualizado a VERIFICADO_PENDIENTE</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3626,7 +3725,7 @@
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3775,7 @@
           <t>Caso cerrado como falso con 0 pts</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3713,7 +3812,7 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3862,7 @@
           <t>Contador incrementado a 1 y caso retornado</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3800,7 +3899,7 @@
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3949,7 @@
           <t>Cierre automático en 3.er fallo verificado</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3887,7 +3986,7 @@
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -3937,7 +4036,7 @@
           <t>Transacción atómica exitosa; saldo final = 350 pts</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -3974,7 +4073,7 @@
       </c>
       <c r="Q34" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4123,7 @@
           <t>HTTP 400 recibido; puntos bloqueados</t>
         </is>
       </c>
-      <c r="J35" s="8" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -4061,7 +4160,7 @@
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4210,7 @@
           <t>Caso retornado a bolsa en estado APROBADO</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -4148,7 +4247,7 @@
       </c>
       <c r="Q36" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4297,7 @@
           <t>Retorno como EN_SANEAMIENTO confirmado</t>
         </is>
       </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -4235,7 +4334,7 @@
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4384,7 @@
           <t>Caso en RESUELTO_TECNICO; agente libre</t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -4322,7 +4421,7 @@
       </c>
       <c r="Q38" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4471,7 @@
           <t>Caso cerrado definitivamente en RESUELTO</t>
         </is>
       </c>
-      <c r="J39" s="8" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -4409,7 +4508,7 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4558,7 @@
           <t>Caso devuelto a EN_SANEAMIENTO con observaciones</t>
         </is>
       </c>
-      <c r="J40" s="8" t="inlineStr">
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -4496,7 +4595,7 @@
       </c>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4646,7 @@
           <t>Producto creado y actualizado en catálogo</t>
         </is>
       </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -4584,7 +4683,7 @@
       </c>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4733,7 @@
           <t>Baja lógica confirmada; cero errores de FK</t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -4671,7 +4770,7 @@
       </c>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4821,7 @@
           <t>Suma en vivo calculada exactamente en 350 pts</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -4759,7 +4858,7 @@
       </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4908,7 @@
           <t>Botón bloqueado y aviso mostrado</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -4846,7 +4945,7 @@
       </c>
       <c r="Q44" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4995,7 @@
           <t>Bloqueo verificado con mensaje de puntos faltantes</t>
         </is>
       </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -4933,7 +5032,7 @@
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -4983,7 +5082,7 @@
           <t>Revalidación de precio ejecutada con éxito</t>
         </is>
       </c>
-      <c r="J46" s="8" t="inlineStr">
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5020,7 +5119,7 @@
       </c>
       <c r="Q46" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5169,7 @@
           <t>Reserva TTL creada y stock provisional reducido a 3</t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5107,7 +5206,7 @@
       </c>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5256,7 @@
           <t>1 éxito, 1 conflicto 409; cero sobreventa (tras fix atómico en BUG-102)</t>
         </is>
       </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5194,7 +5293,7 @@
       </c>
       <c r="Q48" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5343,7 @@
           <t>Stock restaurado en BD tras 5 minutos</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5281,7 +5380,7 @@
       </c>
       <c r="Q49" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5430,7 @@
           <t>HTTP 201 Created; código ECO-7142-N emitido</t>
         </is>
       </c>
-      <c r="J50" s="8" t="inlineStr">
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5368,7 +5467,7 @@
       </c>
       <c r="Q50" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5519,7 @@
           <t>Entrega confirmada y pedido cerrado exitosamente</t>
         </is>
       </c>
-      <c r="J51" s="8" t="inlineStr">
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5457,7 +5556,7 @@
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5607,7 @@
           <t>Banners con textos exactos mostrados</t>
         </is>
       </c>
-      <c r="J52" s="8" t="inlineStr">
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5545,7 +5644,7 @@
       </c>
       <c r="Q52" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5694,7 @@
           <t>Stock reintegrado y puntos retenidos según directiva</t>
         </is>
       </c>
-      <c r="J53" s="8" t="inlineStr">
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5632,7 +5731,7 @@
       </c>
       <c r="Q53" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5781,7 @@
           <t>AsyncStorage medido en 45 ms; API en 190 ms promedio</t>
         </is>
       </c>
-      <c r="J54" s="8" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5719,7 +5818,7 @@
       </c>
       <c r="Q54" s="4" t="inlineStr">
         <is>
-          <t>Dev Backend &amp; BD</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5868,7 @@
           <t>10/10 imágenes comprimidas entre 750 KB y 1.15 MB</t>
         </is>
       </c>
-      <c r="J55" s="8" t="inlineStr">
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5806,7 +5905,7 @@
       </c>
       <c r="Q55" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5956,7 @@
           <t>401 y 403 devueltos exactamente</t>
         </is>
       </c>
-      <c r="J56" s="8" t="inlineStr">
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5894,7 +5993,7 @@
       </c>
       <c r="Q56" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -5944,7 +6043,7 @@
           <t>Bloqueo exitoso; una única petición HTTP efectuada</t>
         </is>
       </c>
-      <c r="J57" s="8" t="inlineStr">
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -5981,7 +6080,7 @@
       </c>
       <c r="Q57" s="4" t="inlineStr">
         <is>
-          <t>Dev Frontend Mobile UI/UX</t>
+          <t>Rodriguez Iván / Kuhn Joaquin</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6130,7 @@
           <t>Spinner mostrado fluidamente</t>
         </is>
       </c>
-      <c r="J58" s="8" t="inlineStr">
+      <c r="J58" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -6068,7 +6167,7 @@
       </c>
       <c r="Q58" s="4" t="inlineStr">
         <is>
-          <t>Dev Frontend Mobile UI/UX</t>
+          <t>Rodriguez Iván / Kuhn Joaquin</t>
         </is>
       </c>
     </row>
@@ -6102,91 +6201,91 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="36" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID del Caso</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Funcionalidad a testar</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Precondiciones</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Datos de prueba</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Pasos a ejecutar</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Resultado esperado</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Resultado Real</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Postcondiciones</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Evidencia</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>ID Requerimiento</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Herramienta</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Tipo de prueba</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>Responsable Corrección Bug</t>
         </is>
@@ -6276,7 +6375,7 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6463,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6551,7 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6639,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6727,7 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6815,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6902,7 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6989,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -6977,7 +7076,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7164,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -7152,7 +7251,7 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7338,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7425,7 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7512,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7599,7 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>Dev Backend &amp; BD</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7686,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7773,7 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>Dev Frontend Mobile UI/UX</t>
+          <t>Rodriguez Iván / Kuhn Joaquin</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7860,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>Dev Frontend Mobile UI/UX</t>
+          <t>Rodriguez Iván / Kuhn Joaquin</t>
         </is>
       </c>
     </row>
@@ -7795,91 +7894,91 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID del Caso</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Funcionalidad a testar</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Precondiciones</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Datos de prueba</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Pasos a ejecutar</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Resultado esperado</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Resultado Real</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Postcondiciones</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Evidencia</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>ID Requerimiento</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Herramienta</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Tipo de prueba</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>Responsable Corrección Bug</t>
         </is>
@@ -7970,7 +8069,7 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -8058,7 +8157,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8245,7 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8332,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8420,7 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8507,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8594,7 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8681,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8768,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8855,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8942,7 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -8931,7 +9030,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9117,7 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9204,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9291,7 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9378,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9465,7 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -9453,7 +9552,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9639,7 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -9627,7 +9726,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -9714,7 +9813,7 @@
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9900,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9988,7 @@
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -9976,7 +10075,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10164,7 @@
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10252,7 @@
       </c>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -10241,7 +10340,7 @@
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -10275,91 +10374,91 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID del Caso</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Funcionalidad a testar</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Precondiciones</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Datos de prueba</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Pasos a ejecutar</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Resultado esperado</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Resultado Real</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Postcondiciones</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Evidencia</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>ID Requerimiento</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Herramienta</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Tipo de prueba</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>Responsable Corrección Bug</t>
         </is>
@@ -10448,7 +10547,7 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -10535,7 +10634,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10721,7 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10808,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10895,7 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10982,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -10970,7 +11069,7 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11057,7 +11156,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11091,91 +11190,91 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID del Caso</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Funcionalidad a testar</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Precondiciones</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Datos de prueba</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Pasos a ejecutar</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Resultado esperado</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Resultado Real</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Postcondiciones</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Evidencia</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>ID Requerimiento</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Herramienta</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Tipo de prueba</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>Responsable Corrección Bug</t>
         </is>
@@ -11265,7 +11364,7 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11353,7 +11452,7 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11441,7 +11540,7 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11529,7 +11628,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -11549,63 +11648,63 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID caso</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Ejecutado por</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Evidencia (link)</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Herramienta</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Reintentos / fallos</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Responsable Corrección Bug</t>
         </is>
@@ -11624,10 +11723,10 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -11657,7 +11756,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11674,10 +11773,10 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -11707,7 +11806,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11724,10 +11823,10 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -11757,7 +11856,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11774,10 +11873,10 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -11807,7 +11906,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11824,10 +11923,10 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -11857,7 +11956,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11874,10 +11973,10 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -11907,7 +12006,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11924,10 +12023,10 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -11957,7 +12056,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -11974,10 +12073,10 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12007,7 +12106,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -12024,10 +12123,10 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12057,7 +12156,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -12074,10 +12173,10 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12107,7 +12206,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -12124,10 +12223,10 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12157,7 +12256,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -12174,10 +12273,10 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12207,7 +12306,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -12224,10 +12323,10 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12257,7 +12356,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -12274,10 +12373,10 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12307,7 +12406,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -12324,10 +12423,10 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12357,7 +12456,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -12374,10 +12473,10 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12407,7 +12506,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -12424,10 +12523,10 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12457,7 +12556,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -12474,10 +12573,10 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12507,7 +12606,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -12524,10 +12623,10 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12557,7 +12656,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -12574,10 +12673,10 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12607,7 +12706,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -12624,10 +12723,10 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12657,7 +12756,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -12674,10 +12773,10 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12707,7 +12806,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -12724,10 +12823,10 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12757,7 +12856,7 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -12774,10 +12873,10 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12807,7 +12906,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -12824,10 +12923,10 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12857,7 +12956,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -12874,10 +12973,10 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12907,7 +13006,7 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -12924,10 +13023,10 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -12957,7 +13056,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -12974,10 +13073,10 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13007,7 +13106,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13024,10 +13123,10 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13057,7 +13156,7 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13074,10 +13173,10 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13107,7 +13206,7 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13124,10 +13223,10 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13157,7 +13256,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13174,10 +13273,10 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13207,7 +13306,7 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13224,10 +13323,10 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13257,7 +13356,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13274,10 +13373,10 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13307,7 +13406,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13324,10 +13423,10 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13357,7 +13456,7 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13374,10 +13473,10 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13407,7 +13506,7 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13424,10 +13523,10 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13457,7 +13556,7 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13474,10 +13573,10 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13507,7 +13606,7 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13524,10 +13623,10 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13557,7 +13656,7 @@
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -13574,10 +13673,10 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13607,7 +13706,7 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -13624,10 +13723,10 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13657,7 +13756,7 @@
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -13674,10 +13773,10 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13707,7 +13806,7 @@
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -13724,10 +13823,10 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13757,7 +13856,7 @@
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -13774,10 +13873,10 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13807,7 +13906,7 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -13824,10 +13923,10 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13857,7 +13956,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -13874,10 +13973,10 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13907,7 +14006,7 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -13924,10 +14023,10 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -13957,7 +14056,7 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -13974,10 +14073,10 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14007,7 +14106,7 @@
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -14024,10 +14123,10 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14057,7 +14156,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -14074,10 +14173,10 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14107,7 +14206,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -14124,10 +14223,10 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14157,7 +14256,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -14174,10 +14273,10 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14207,7 +14306,7 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -14224,10 +14323,10 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14257,7 +14356,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>Dev Backend &amp; BD</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -14274,10 +14373,10 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14307,7 +14406,7 @@
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -14324,10 +14423,10 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14357,7 +14456,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -14374,10 +14473,10 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14407,7 +14506,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>Dev Frontend Mobile UI/UX</t>
+          <t>Rodriguez Iván / Kuhn Joaquin</t>
         </is>
       </c>
     </row>
@@ -14424,10 +14523,10 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Raul Escobar (Lead QA)</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
+          <t>Benitez Facundo (Analista de QA)</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14457,7 +14556,7 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>Dev Frontend Mobile UI/UX</t>
+          <t>Rodriguez Iván / Kuhn Joaquin</t>
         </is>
       </c>
     </row>
@@ -14488,76 +14587,76 @@
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID Requerimiento</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>ID Caso de Prueba</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Descripción Prueba</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Funcionalidad a Testar</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Evidencia</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Herramienta</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Módulo</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Estado de Ejecución</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>ID Defecto (Bug)</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Severidad</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Estado Defecto</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Responsable Corrección</t>
         </is>
@@ -14609,7 +14708,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14631,7 +14730,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14780,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14703,7 +14802,7 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -14753,7 +14852,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14775,7 +14874,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -14825,7 +14924,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14847,7 +14946,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14996,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14919,7 +15018,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -14969,7 +15068,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -14991,7 +15090,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -15041,7 +15140,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15063,7 +15162,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15212,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15135,7 +15234,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15284,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15207,7 +15306,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -15257,7 +15356,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15279,7 +15378,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15428,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15351,7 +15450,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15500,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15423,7 +15522,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -15473,7 +15572,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15495,7 +15594,7 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -15545,7 +15644,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15567,7 +15666,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -15617,7 +15716,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15639,7 +15738,7 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15788,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15711,7 +15810,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15860,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15783,7 +15882,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -15833,7 +15932,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15855,7 +15954,7 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -15905,7 +16004,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15927,7 +16026,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -15977,7 +16076,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -15999,7 +16098,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -16049,7 +16148,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16071,7 +16170,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16121,7 +16220,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16143,7 +16242,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16292,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16215,7 +16314,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16265,7 +16364,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16287,7 +16386,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16337,7 +16436,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16359,7 +16458,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16409,7 +16508,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16431,7 +16530,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16481,7 +16580,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16503,7 +16602,7 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16652,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16575,7 +16674,7 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16625,7 +16724,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16647,7 +16746,7 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16697,7 +16796,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16719,7 +16818,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16769,7 +16868,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16791,7 +16890,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16940,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16863,7 +16962,7 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2B (Triaje &amp; Agente Campo)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16913,7 +17012,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -16935,7 +17034,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -16985,7 +17084,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J35" s="8" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17007,7 +17106,7 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17156,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17079,7 +17178,7 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -17129,7 +17228,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17151,7 +17250,7 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -17201,7 +17300,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17223,7 +17322,7 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -17273,7 +17372,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J39" s="8" t="inlineStr">
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17295,7 +17394,7 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17444,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J40" s="8" t="inlineStr">
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17367,7 +17466,7 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2C (Saneamiento &amp; Puntos)</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17516,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17439,7 +17538,7 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -17489,7 +17588,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17511,7 +17610,7 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -17561,7 +17660,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17583,7 +17682,7 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17732,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17655,7 +17754,7 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -17705,7 +17804,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17727,7 +17826,7 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -17777,7 +17876,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J46" s="8" t="inlineStr">
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17799,7 +17898,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -17849,7 +17948,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17871,7 +17970,7 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -17921,7 +18020,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -17943,7 +18042,7 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -17993,7 +18092,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -18015,7 +18114,7 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -18065,7 +18164,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J50" s="8" t="inlineStr">
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -18087,7 +18186,7 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3A (Tienda &amp; Carrito)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -18137,7 +18236,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J51" s="8" t="inlineStr">
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -18159,7 +18258,7 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -18209,7 +18308,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J52" s="8" t="inlineStr">
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -18231,7 +18330,7 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -18281,7 +18380,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J53" s="8" t="inlineStr">
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -18303,7 +18402,7 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 3B (Colaborador &amp; Entrega)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -18353,7 +18452,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J54" s="8" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -18375,7 +18474,7 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>Dev Backend &amp; BD</t>
+          <t>Benitez Angel (BackEnd)</t>
         </is>
       </c>
     </row>
@@ -18425,7 +18524,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J55" s="8" t="inlineStr">
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -18447,7 +18546,7 @@
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 2A (Reporte Ciudadano)</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18596,7 @@
           <t>Negativo</t>
         </is>
       </c>
-      <c r="J56" s="8" t="inlineStr">
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -18519,7 +18618,7 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>Dev Módulo 1 (Auth &amp; RBAC)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18668,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J57" s="8" t="inlineStr">
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -18591,7 +18690,7 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>Dev Frontend Mobile UI/UX</t>
+          <t>Rodriguez Iván / Kuhn Joaquin</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18740,7 @@
           <t>Positivo</t>
         </is>
       </c>
-      <c r="J58" s="8" t="inlineStr">
+      <c r="J58" s="9" t="inlineStr">
         <is>
           <t>Pasó</t>
         </is>
@@ -18663,7 +18762,7 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>Dev Frontend Mobile UI/UX</t>
+          <t>Rodriguez Iván / Kuhn Joaquin</t>
         </is>
       </c>
     </row>
@@ -18695,64 +18794,64 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Fase</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Módulo</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Requisito / Storyboard / Criterios BDD</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>Casos Asociados</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>Jest</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Postman</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Pytest</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Cypress</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>HU-INV-01</t>
         </is>
@@ -18799,7 +18898,7 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>HU-INV-02</t>
         </is>
@@ -18846,7 +18945,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>HU-INV-03</t>
         </is>
@@ -18893,7 +18992,7 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>RF-AUT-01</t>
         </is>
@@ -18940,7 +19039,7 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>RF-AUT-02</t>
         </is>
@@ -18987,7 +19086,7 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>RF-AUT-03</t>
         </is>
@@ -19034,7 +19133,7 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>RF-AUT-04</t>
         </is>
@@ -19081,7 +19180,7 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>RF-AUT-05</t>
         </is>
@@ -19128,7 +19227,7 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>HU-03</t>
         </is>
@@ -19175,7 +19274,7 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>RF-REP-01</t>
         </is>
@@ -19222,7 +19321,7 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>RF-REP-02</t>
         </is>
@@ -19269,7 +19368,7 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>RF-REP-04</t>
         </is>
@@ -19316,7 +19415,7 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>RF-REP-06</t>
         </is>
@@ -19363,7 +19462,7 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>HU-05</t>
         </is>
@@ -19410,7 +19509,7 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>RF-ADM-03b</t>
         </is>
@@ -19457,7 +19556,7 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>HU-08</t>
         </is>
@@ -19504,7 +19603,7 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>HU-09</t>
         </is>
@@ -19551,7 +19650,7 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>RF-ADM-04</t>
         </is>
@@ -19598,7 +19697,7 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>HU-10</t>
         </is>
@@ -19645,7 +19744,7 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>HU-11</t>
         </is>
@@ -19692,7 +19791,7 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>HU-07</t>
         </is>
@@ -19739,7 +19838,7 @@
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>RF-TIE-01</t>
         </is>
@@ -19786,7 +19885,7 @@
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>RF-TIE-02</t>
         </is>
@@ -19833,7 +19932,7 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>HU-08-TIE</t>
         </is>
@@ -19880,7 +19979,7 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>RF-COL-01</t>
         </is>
@@ -19927,7 +20026,7 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>RF-TIE-06</t>
         </is>
@@ -19974,7 +20073,7 @@
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>RNF-01</t>
         </is>
@@ -20021,7 +20120,7 @@
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>RNF-02</t>
         </is>
@@ -20068,7 +20167,7 @@
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>RNF-07</t>
         </is>
@@ -20115,7 +20214,7 @@
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>RNF-10</t>
         </is>

--- a/docs/testing/EcoAlerta_Testware_Matriz_Casos_Ejecucion.xlsx
+++ b/docs/testing/EcoAlerta_Testware_Matriz_Casos_Ejecucion.xlsx
@@ -895,10 +895,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1061,12 +1061,24 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Estándar de Calidad ISO 25010</t>
+          <t>Modelo de Calidad ISO 25010</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Evaluación formal de los 8 atributos de calidad: Adecuación funcional, Rendimiento, Compatibilidad, Usabilidad, Fiabilidad, Seguridad, Mantenibilidad y Portabilidad.</t>
+          <t>Adopción de ISO/IEC 25010 como marco de referencia metodológica y guía de buenas prácticas de calidad para mantener consistencia, sin pretensión de certificación externa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Respaldo de Evidencias y Packs de Datos</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Cada caso de prueba cuenta con su Request, Response y Pack de Datos exacto registrado en el Dossier de Evidencias (08_DOSSIER_EVIDENCIAS_DE_PRUEBA.md) y en la colección oficial exportada de Postman.</t>
         </is>
       </c>
     </row>

--- a/docs/testing/EcoAlerta_Testware_Matriz_Casos_Ejecucion.xlsx
+++ b/docs/testing/EcoAlerta_Testware_Matriz_Casos_Ejecucion.xlsx
@@ -9,14 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos de Prueba" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos - Jest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos - Postman" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos - Pytest" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos - Cypress" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanillaDeEjecucion" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trazabilidad" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requerimientos" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criterios y Supuestos" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos - Jest y RNTL" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos - Postman y Supertest" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanillaDeEjecucion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trazabilidad" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requerimientos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criterios y Supuestos" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -889,204 +887,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Tema</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>Definición y Criterio Establecido</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Alcance de Pruebas</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Cobertura derivada al 100% de la lista de Requisitos Funcionales (47) y No Funcionales (21) de EcoAlerta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Ambiente de Pruebas</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Backend Node.js v24 con TypeScript v5, base de datos de test SQLite/PostgreSQL aislada con Prisma ORM, cliente móvil React Native Expo SDK 52.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Convención de Rutas API</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Rutas REST bajo prefijo /api/: /auth/register, /auth/login, /denuncias, /productos, /canjes, /sucursales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Datos de Prueba Deterministas</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Uso de fixtures controlados y semillas predecibles (npm run prisma:seed) para garantizar reproducibilidad exacta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Política de Corrección de Bugs</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>El responsable exclusivo de analizar, depurar y corregir los defectos es el mismo desarrollador que implementó el módulo o función.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Gestión de Concurrencia</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Validación estricta de atomicidad mediante transacciones prisma.$transaction en toma 1 a 1 de casos y reserva de stock TTL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Política de Ecopuntos</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Los puntos solo se acreditan cuando el Administrador confirma la veracidad del foco ambiental en terreno. Nunca se otorgan en la creación inicial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Política de Expiración de Canjes</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Los pedidos no retirados tras 30 días corridos pasan a EXPIRADO; el stock vuelve al inventario y los puntos NO se reembolsan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Protocolo de Inaccesibilidad</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Se toleran hasta 3 visitas con aviso municipal pegado. Al 3.er intento fallido el caso se cierra como CERRADO_INACCESIBLE para derivación legal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Compresión Multimedia (RNF-02)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Toda fotografía debe procesarse en cliente reduciendo su peso obligatoriamente a &lt; 1.2 MB antes de cualquier transferencia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>Feedback Transaccional (RNF-10)</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Toda mutación a base de datos despliega en el ms 0 el TransactionLoaderModal bloqueando toques repetidos del usuario.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Criterios de Aceptación BDD</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Todos los criterios de aceptación se redactan y validan formalmente en sintaxis Gherkin (Dado / Cuando / Entonces).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Modelo de Calidad ISO 25010</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Adopción de ISO/IEC 25010 como marco de referencia metodológica y guía de buenas prácticas de calidad para mantener consistencia, sin pretensión de certificación externa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Respaldo de Evidencias y Packs de Datos</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Cada caso de prueba cuenta con su Request, Response y Pack de Datos exacto registrado en el Dossier de Evidencias (08_DOSSIER_EVIDENCIAS_DE_PRUEBA.md) y en la colección oficial exportada de Postman.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1109,7 +909,7 @@
     <col width="47" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="33" customWidth="1" min="17" max="17"/>
@@ -1887,7 +1687,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -2151,7 +1951,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -2239,7 +2039,7 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -2850,7 +2650,7 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -3373,7 +3173,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -3548,7 +3348,7 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
@@ -3983,7 +3783,7 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
@@ -4331,7 +4131,7 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
@@ -4767,7 +4567,7 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
@@ -5116,7 +4916,7 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
@@ -5290,7 +5090,7 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
@@ -5728,7 +5528,7 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
@@ -6194,7 +5994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6570,941 +6370,945 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>CP-RF-AUT-04-01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Enrutamiento dinámico según rol (CITIZEN, AGENT, ADMIN, COLLABORATOR)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>RF-AUT-04 · Navegación React Navigation</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>4 usuarios de prueba con cada uno de los roles</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Tokens válidos para cada rol</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>1. Iniciar sesión con cada rol.
+2. Validar pantalla inicial de aterrizaje.</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>CITIZEN -&gt; CitizenHomeScreen, AGENT -&gt; AgentHomeScreen, ADMIN -&gt; AdminDenunciasScreen, COLLABORATOR -&gt; CollaboratorDeliveryScreen</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Navegación determinista según rol verificada</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Entorno cargado según perfil</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>E2E-NAV-ROLES-01</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>RF-AUT-04</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>Jest (RNTL)</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>CP-RF-AUT-05-01</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Persistencia de sesión en AsyncStorage y Logout seguro</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>RF-AUT-05 · AsyncStorage &amp; AuthContext</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Sesión iniciada con token en AsyncStorage</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Llamada a signOut()</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>1. Cerrar y abrir app (mantener sesión).
 2. Presionar Cerrar Sesión en perfil.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Sesión persiste ante reinicio; al hacer logout se borra el token y retorna al Home en Modo Invitado</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Sesión limpiada y redirección a Invitado verificada</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>AsyncStorage libre de credenciales</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>TEST-ASYNC-STORE-01</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>RF-AUT-05</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>Jest</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Unitario / Integración</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>Positivo</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CP-RF-AUT-06-01</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Cold start en Modo Invitado muestra Home explicativo en &lt; 300 ms</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>HU-INV-01 / RF-AUT-06 / RNF-09 · CitizenHomeScreen</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>App sin sesión guardada</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Inicio en frío de la aplicación</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>1. Abrir app desde estado frío.
 2. Medir tiempo de renderizado y contenido.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Renderizado &lt; 300 ms; sin login bloqueante; 3 tarjetas explicativas (Reportá, Saneamiento, Ecopuntos) visibles</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Renderizado en 185 ms; 3 tarjetas visibles</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Usuario en modo lectura</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>PERF-COLD-START-01</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>HU-INV-01</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>Jest</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>UI / Performance</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>Positivo</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AUT-06-02</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Botón CTA de cabecera 'Regístrate para empezar a usar la app'</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>HU-INV-02 / RF-AUT-06 · Header Component</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Usuario en Modo Invitado en Home</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Clic en botón de cabecera</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>1. Verificar texto de botón.
+2. Presionar botón.</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Botón verde con texto exacto; navega a RegisterScreen en &lt; 150 ms</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Texto verificado y navegación fluida</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Pantalla de registro montada</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>UI-CTA-HEADER-01</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>HU-INV-02</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Jest (RNTL)</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AUT-07-01</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Navegación libre en Modo Invitado solo lectura en Tienda</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>HU-INV-03 / RF-AUT-07 · StoreScreen</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Usuario en Modo Invitado</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Navegar a pestaña Tienda</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>1. Abrir Tienda.
+2. Filtrar por categorías y buscar producto.</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Muestra catálogo de productos con precios en puntos; buscador funciona en lectura; no muestra botón de checkout</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Catálogo explorable en modo lectura</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Estado de invitado preservado</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>UI-GUEST-STORE-01</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>RF-AUT-07</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Jest (RNTL)</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>CP-RF-AUT-08-01</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Auth Gate: Bloqueo al presionar botón Cámara / Reportar foco</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>HU-INV-03 / RF-AUT-08 / RNF-09 · AuthGateModal</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Usuario en Modo Invitado</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Toque en botón central Cámara</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>1. Presionar botón Cámara en barra inferior.
 2. Medir tiempo de modal.</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Cámara no se abre; modal 'Acción protegida' aparece en &lt; 100 ms: 'Debes registrarte o iniciar sesión para poder reportar focos ambientales y canjear premios ecológicos.'</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Modal desplegado en 42 ms sin abrir hardware</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>App protegida contra accesos no autenticados</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>SEC-AUTH-GATE-01</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>RF-AUT-08</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>Jest</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>Negativo</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AUT-08-02</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Auth Gate: Bloqueo al presionar 'Agregar al Carrito' en Tienda</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>HU-INV-03 / RF-AUT-08 · ProductDetailScreen</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Usuario invitado viendo un producto</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Toque en botón 'Agregar al Carrito'</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>1. Presionar botón de carrito en producto.</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Ítem no se agrega al carrito; modal 'Acción protegida' desplegado</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Modal mostrado; carrito vacío</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>Carrito permanece en 0</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>SEC-AUTH-GATE-02</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-08</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>Jest</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AUT-08-03</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Auth Gate: Bloqueo al intentar ingresar a Perfil / Historial</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>HU-INV-03 / RF-AUT-08 · ProfileScreen</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Usuario invitado en barra inferior</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Toque en pestaña Perfil</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>1. Tocar pestaña Perfil.</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>No permite ver datos privados; modal 'Acción protegida' desplegado</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Acceso denegado con modal protegido</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>Privacidad preservada</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>SEC-AUTH-GATE-03</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-08</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>Jest</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-REP-02-01</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Compresión obligatoria de foto de cámara a buffer &lt; 1.2 MB</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>RF-REP-02 / RNF-02 · imageCompressor.ts</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Buffer de foto de 4.85 MB (4000x3000px)</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Llamada a compressImage(buffer, {maxSizeMB: 1.2, maxWidth: 1080})</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>1. Procesar imagen de alta resolución con módulo de compresión.</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Buffer comprimido &lt; 1.2 MB (1.258.291 bytes) y ancho &lt;= 1080px sin pérdida de aspecto</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Imagen reducida a 865 KB y 1080px (tras fix de algoritmo en BUG-101)</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Imagen lista para subida</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>TEST-COMPRESS-01</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>RF-REP-02</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>Jest</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>Unitario / Integración</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>CP-RF-AUT-08-02</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Auth Gate: Bloqueo al presionar 'Agregar al Carrito' en Tienda</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>HU-INV-03 / RF-AUT-08 · ProductDetailScreen</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Usuario invitado viendo un producto</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Toque en botón 'Agregar al Carrito'</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>1. Presionar botón de carrito en producto.</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Ítem no se agrega al carrito; modal 'Acción protegida' desplegado</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Modal mostrado; carrito vacío</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Carrito permanece en 0</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>SEC-AUTH-GATE-02</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>RF-AUT-08</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>Jest</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AUT-08-03</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Auth Gate: Bloqueo al intentar ingresar a Perfil / Historial</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>HU-INV-03 / RF-AUT-08 · ProfileScreen</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Usuario invitado en barra inferior</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Toque en pestaña Perfil</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>1. Tocar pestaña Perfil.</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>No permite ver datos privados; modal 'Acción protegida' desplegado</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Acceso denegado con modal protegido</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Privacidad preservada</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>SEC-AUTH-GATE-03</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>RF-AUT-08</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>Jest</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-REP-02-01</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Compresión obligatoria de foto de cámara a buffer &lt; 1.2 MB</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>RF-REP-02 / RNF-02 · imageCompressor.ts</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Buffer de foto de 4.85 MB (4000x3000px)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Llamada a compressImage(buffer, {maxSizeMB: 1.2, maxWidth: 1080})</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>1. Procesar imagen de alta resolución con módulo de compresión.</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Buffer comprimido &lt; 1.2 MB (1.258.291 bytes) y ancho &lt;= 1080px sin pérdida de aspecto</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Imagen reducida a 865 KB y 1080px (tras fix de algoritmo en BUG-101)</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Imagen lista para subida</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>TEST-COMPRESS-01</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>RF-REP-02</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Jest</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>Unitario / Integración</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván (FrontEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AGE-01-01</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Visualización de casos en bolsa con semáforo de prioridad</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>HU-08 / RF-AGE-01 · AgentHomeScreen</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Agente autenticado en servicio</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Abrir bandeja de casos aprobados</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>1. Cargar bolsa de casos.
+2. Validar orden y colores.</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Casos ordenados por severidad; Rojo (Urgente), Naranja (Alta), Amarillo (Media), Verde (Baja); muestra distancia GPS</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Bolsa renderizada con semáforos correctos</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Agente informado de prioridades</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>UI-BOLSA-CASOS-01</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-01</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Jest (RNTL)</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>UI / E2E</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>CP-RF-TIE-02-01</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Cálculo reactivo en vivo de totales de carrito: Total = Sum(Cant * Pts)</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>RF-TIE-02 / RF-TIE-03 · CartContext.tsx</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>2 productos agregados: P1 (100 pts x 2) y P2 (150 pts x 1)</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Operaciones en carrito móvil</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>1. Agregar 2 unidades de P1 y 1 unidad de P2.
 2. Validar suma total.</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>TotalPuntos se actualiza en vivo a 350 pts; persistencia en AsyncStorage; badge de cabecera muestra 3 ítems</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Suma en vivo calculada exactamente en 350 pts</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Carrito listo para checkout</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>TEST-CART-SUM-01</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>RF-TIE-02</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>Jest</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>Unitario / Integración</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-TIE-03-01</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Restricción de agregar más unidades que el stock disponible</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>RF-TIE-03 · ProductDetailScreen</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Producto con stock = 2; carrito tiene 2 unidades</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Intento de presionar botón +</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>1. Tocar botón + en cantidad.</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Botón + pasa a deshabilitado; cantidad se mantiene en 2; aviso: 'Máximo stock disponible alcanzado'</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>Botón bloqueado y aviso mostrado</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>No permite sobrecompra local</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>TEST-CART-LIMIT-01</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>RF-TIE-03</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>Jest</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>UI / Validación</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-TIE-04-01</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Bloqueo de Checkout si puntosUsuario &lt; TotalPuntosCarrito</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>HU-08 / RF-TIE-04 · CheckoutScreen</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Ciudadano con saldo = 80 pts; total carrito = 150 pts</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Intento de confirmar canje</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>1. Abrir Checkout con saldo insuficiente.</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Botón confirmar deshabilitado; texto en rojo: 'Puntos insuficientes. Te faltan 70 puntos para este canje.'; no envía petición a red</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Bloqueo verificado con mensaje de puntos faltantes</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Saldo y stock intactos</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261026-02</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>RF-TIE-04</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>Jest</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>UI / Validación</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-TIE-05-01</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Checkout: Reserva temporal de stock por 5 minutos (TTL)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>HU-08 / RF-TIE-05 · POST /api/canjes/reservar</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Producto con stock = 5; ciudadano con puntos</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>{"productoId":"prod-1","cantidad":2}</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>1. Enviar solicitud de reserva de 2 unidades.</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; reserva creada con estado RESERVADO_PENDIENTE; bloqueadoHasta = now() + 5 min; stock disponible público baja a 3; cuenta regresiva 05:00 en app</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Reserva TTL creada y stock provisional reducido a 3</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Stock protegido durante 5 minutos</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>TEST-TTL-RESERVA-01</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>RF-TIE-05</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>Jest</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>Concurrencia / Resiliencia</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-TIE-05-03</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Expiración automática de reserva tras 5 minutos sin confirmación</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>HU-08 / RF-TIE-05 · cleanExpiredReservations()</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Reserva activa con 5 min transcurridos sin confirmar</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Paso del temporizador a 5m 1s</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>1. Ejecutar worker limpiador de reservas vencidas.</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Reserva pasa a EXPIRADA_LIBERADA; las unidades se reintegran automáticamente al stock disponible del producto; si el usuario intenta confirmar se notifica expiración</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Stock restaurado en BD tras 5 minutos</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Inventario liberado</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>TEST-EXPIRE-TTL-01</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>RF-TIE-05</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -7531,47 +7335,47 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>CP-RNF-01-01</t>
+          <t>CP-RF-TIE-03-01</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Latencia local &lt; 300 ms y API &lt; 600 ms</t>
+          <t>Restricción de agregar más unidades que el stock disponible</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>RNF-01 · Rendimiento general</t>
+          <t>RF-TIE-03 · ProductDetailScreen</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ambiente Staging bajo carga nominal</t>
+          <t>Producto con stock = 2; carrito tiene 2 unidades</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Llamadas a AsyncStorage y endpoints REST</t>
+          <t>Intento de presionar botón +</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>1. Medir latencia en 50 transacciones.</t>
+          <t>1. Tocar botón + en cantidad.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>AsyncStorage completa en &lt; 300 ms; API responde en &lt; 600 ms bajo condiciones normales</t>
+          <t>Botón + pasa a deshabilitado; cantidad se mantiene en 2; aviso: 'Máximo stock disponible alcanzado'</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>AsyncStorage medido en 45 ms; API en 190 ms promedio</t>
+          <t>Botón bloqueado y aviso mostrado</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -7581,17 +7385,17 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>SLA cumplido holgadamente</t>
+          <t>No permite sobrecompra local</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>PERF-LATENCY-01</t>
+          <t>TEST-CART-LIMIT-01</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>RNF-01</t>
+          <t>RF-TIE-03</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -7601,64 +7405,64 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>UI / Validación</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Negativo</t>
         </is>
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>Benitez Angel (BackEnd)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>CP-RNF-02-01</t>
+          <t>CP-RF-TIE-04-01</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Compresión de fotos raw de 12 MP garantizada &lt; 1.2 MB</t>
+          <t>Bloqueo de Checkout si puntosUsuario &lt; TotalPuntosCarrito</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>RNF-02 · Compresión multimedia</t>
+          <t>HU-08 / RF-TIE-04 · CheckoutScreen</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Set de 10 imágenes raw de 12 MP</t>
+          <t>Ciudadano con saldo = 80 pts; total carrito = 150 pts</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Paso por pipeline de compresión</t>
+          <t>Intento de confirmar canje</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>1. Procesar set de imágenes.</t>
+          <t>1. Abrir Checkout con saldo insuficiente.</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>El 100% de las imágenes resultan con peso &lt; 1.2 MB y resolución max 1080px</t>
+          <t>Botón confirmar deshabilitado; texto en rojo: 'Puntos insuficientes. Te faltan 70 puntos para este canje.'; no envía petición a red</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>10/10 imágenes comprimidas entre 750 KB y 1.15 MB</t>
+          <t>Bloqueo verificado con mensaje de puntos faltantes</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -7668,17 +7472,17 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Cero desbordes de tamaño</t>
+          <t>Saldo y stock intactos</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>TEST-COMPRESS-RAW-01</t>
+          <t>LOG-API-20261026-02</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>RNF-02</t>
+          <t>RF-TIE-04</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -7688,64 +7492,64 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>Unitario / Integración</t>
+          <t>UI / Validación</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Negativo</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>Rodriguez Iván (FrontEnd)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>CP-RNF-10-01</t>
+          <t>CP-RF-TIE-05-01</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>TransactionLoaderModal bloquea UI en mutaciones evitando doble toque</t>
+          <t>Checkout: Reserva temporal de stock por 5 minutos (TTL)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>RNF-10 · TransactionLoaderModal.tsx</t>
+          <t>HU-08 / RF-TIE-05 · POST /api/canjes/reservar</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Formulario listo para enviar</t>
+          <t>Producto con stock = 5; ciudadano con puntos</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Simular 5 toques rápidos en botón confirmar</t>
+          <t>{"productoId":"prod-1","cantidad":2}</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>1. Presionar botón repetidamente en &lt; 1s.</t>
+          <t>1. Enviar solicitud de reserva de 2 unidades.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Modal bloquea pantalla en el ms 0; se envía una única petición a red; se cierra al responder la API sin recargas redundantes</t>
+          <t>HTTP 200 OK; reserva creada con estado RESERVADO_PENDIENTE; bloqueadoHasta = now() + 5 min; stock disponible público baja a 3; cuenta regresiva 05:00 en app</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Bloqueo exitoso; una única petición HTTP efectuada</t>
+          <t>Reserva TTL creada y stock provisional reducido a 3</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -7755,17 +7559,17 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Cero duplicación de transacciones</t>
+          <t>Stock protegido durante 5 minutos</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>UI-LOCK-MODAL-01</t>
+          <t>TEST-TTL-RESERVA-01</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>RNF-10</t>
+          <t>RF-TIE-05</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -7775,7 +7579,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>UI / Resiliencia</t>
+          <t>Concurrencia / Resiliencia</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
@@ -7785,92 +7589,440 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>Rodriguez Iván / Kuhn Joaquin</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>CP-RF-TIE-05-03</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Expiración automática de reserva tras 5 minutos sin confirmación</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>HU-08 / RF-TIE-05 · cleanExpiredReservations()</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Reserva activa con 5 min transcurridos sin confirmar</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Paso del temporizador a 5m 1s</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>1. Ejecutar worker limpiador de reservas vencidas.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Reserva pasa a EXPIRADA_LIBERADA; las unidades se reintegran automáticamente al stock disponible del producto; si el usuario intenta confirmar se notifica expiración</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Stock restaurado en BD tras 5 minutos</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Inventario liberado</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>TEST-EXPIRE-TTL-01</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>RF-TIE-05</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Jest</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Unitario / Integración</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>CP-RNF-01-01</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Latencia local &lt; 300 ms y API &lt; 600 ms</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>RNF-01 · Rendimiento general</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Ambiente Staging bajo carga nominal</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Llamadas a AsyncStorage y endpoints REST</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>1. Medir latencia en 50 transacciones.</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>AsyncStorage completa en &lt; 300 ms; API responde en &lt; 600 ms bajo condiciones normales</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>AsyncStorage medido en 45 ms; API en 190 ms promedio</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>SLA cumplido holgadamente</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>PERF-LATENCY-01</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>RNF-01</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Jest</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>CP-RNF-02-01</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Compresión de fotos raw de 12 MP garantizada &lt; 1.2 MB</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>RNF-02 · Compresión multimedia</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Set de 10 imágenes raw de 12 MP</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Paso por pipeline de compresión</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>1. Procesar set de imágenes.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>El 100% de las imágenes resultan con peso &lt; 1.2 MB y resolución max 1080px</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>10/10 imágenes comprimidas entre 750 KB y 1.15 MB</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Cero desbordes de tamaño</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>TEST-COMPRESS-RAW-01</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>RNF-02</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Jest</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Unitario / Integración</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván (FrontEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>CP-RNF-10-01</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>TransactionLoaderModal bloquea UI en mutaciones evitando doble toque</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>RNF-10 · TransactionLoaderModal.tsx</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Formulario listo para enviar</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Simular 5 toques rápidos en botón confirmar</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>1. Presionar botón repetidamente en &lt; 1s.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Modal bloquea pantalla en el ms 0; se envía una única petición a red; se cierra al responder la API sin recargas redundantes</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Bloqueo exitoso; una única petición HTTP efectuada</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Cero duplicación de transacciones</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>UI-LOCK-MODAL-01</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>RNF-10</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Jest</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>UI / Resiliencia</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Kuhn Joaquin</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>CP-RNF-10-02</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Spinner contextual (ActivityIndicator) en filtros de listas</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>RNF-10 · Filtros y Chips</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Pantalla de denuncias o tienda con lista cargada</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Cambiar filtro de categoría o prioridad</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>1. Presionar chip de filtro.</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Se muestra inmediatamente un ActivityIndicator con mensaje 'Filtrando resultados...' hasta renderizar la nueva lista sin congelamiento</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Spinner mostrado fluidamente</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Feedback continuo</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>UI-SPINNER-CHIPS-01</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>RNF-10</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>Jest</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>UI / Feedback</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>Positivo</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>Rodriguez Iván / Kuhn Joaquin</t>
         </is>
@@ -7887,7 +8039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7901,2489 +8053,9 @@
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="33" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>ID del Caso</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>Prioridad</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>Funcionalidad a testar</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>Precondiciones</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>Datos de prueba</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>Pasos a ejecutar</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>Resultado esperado</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>Resultado Real</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="K1" s="10" t="inlineStr">
-        <is>
-          <t>Postcondiciones</t>
-        </is>
-      </c>
-      <c r="L1" s="10" t="inlineStr">
-        <is>
-          <t>Evidencia</t>
-        </is>
-      </c>
-      <c r="M1" s="10" t="inlineStr">
-        <is>
-          <t>ID Requerimiento</t>
-        </is>
-      </c>
-      <c r="N1" s="10" t="inlineStr">
-        <is>
-          <t>Herramienta</t>
-        </is>
-      </c>
-      <c r="O1" s="10" t="inlineStr">
-        <is>
-          <t>Tipo de prueba</t>
-        </is>
-      </c>
-      <c r="P1" s="10" t="inlineStr">
-        <is>
-          <t>Escenario</t>
-        </is>
-      </c>
-      <c r="Q1" s="10" t="inlineStr">
-        <is>
-          <t>Responsable Corrección Bug</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AUT-01-01</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Flujo nominal — Registro del ciudadano con rol CITIZEN y balance 0</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-01 · POST /api/auth/register</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>BD limpia; correo sin registrar</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>{"nombre":"Carlos Alberto Gómez","email":"ciudadano.valido@ecoalerta.gob.ar","password":"PasswordEco2026!"}</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>1. Enviar POST /api/auth/register con payload válido.
-2. Validar HTTP status.
-3. Validar rol y puntos en BD.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 201 Created; token JWT emitido; user.rol='CITIZEN', puntos=0; redirección a CitizenHomeScreen</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 201 Created; token válido; rol CITIZEN asignado con 0 puntos</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>Usuario persistido en BD</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261024-01</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-01</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q2" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AUT-01-02</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Rechazo de registro ante correo electrónico duplicado</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-02 · POST /api/auth/register</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Usuario ya registrado con correo vecino.registrado@pilar.gob.ar</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>{"nombre":"Esteban Quito","email":"vecino.registrado@pilar.gob.ar","password":"ClaveSegura123!"}</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>1. Enviar POST /api/auth/register con correo ya existente.
-2. Validar respuesta de error.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 409 Conflict; mensaje: 'El correo electrónico ya se encuentra registrado.'</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 409 Conflict recibido con mensaje exacto</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>No se crea registro duplicado</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261024-02</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-02</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AUT-03-01</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Login exitoso con credenciales válidas y emisión de JWT</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-03 · POST /api/auth/login</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Usuario maria.agente@pilar.gob.ar activo con rol AGENT</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>{"identifier":"maria.agente@pilar.gob.ar","password":"ClaveAgente1!"}</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>1. Enviar POST /api/auth/login con credenciales válidas.
-2. Validar JWT y datos de usuario.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; token JWT firmado retornado; payload incluye {id, rol:'AGENT'}</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; token emitido correctamente</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>Token almacenado en cliente</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261024-03</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-03</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AUT-03-02</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Login fallido por contraseña errónea</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-03 · POST /api/auth/login</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Usuario admin@pilar.gob.ar existente</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>{"identifier":"admin@pilar.gob.ar","password":"ClaveEquivocada999"}</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>1. Enviar POST /api/auth/login con contraseña inválida.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 401 Unauthorized; mensaje: 'Credenciales inválidas'; banner rojo en UI: 'El correo electrónico o la contraseña son incorrectos. Por favor, verifica tus datos.'</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 401 recibido y banner rojo desplegado</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>Sesión no iniciada</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261024-04</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-03</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-REP-01-01</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Creación exitosa de reporte ciudadano con GPS y foto comprimida</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>HU-03 / RF-REP-01 / RF-REP-04 · POST /api/denuncias</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Ciudadano autenticado con token válido</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>{"categoria":"BASURAL","descripcion":"Microbasural clandestino","latitud":-34.4586,"longitud":-58.9142,"direccion":"Las Palmeras 1230","fotoUrl":"data:image/jpeg..."}</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>1. Enviar reporte con datos completos.
-2. Validar HTTP 201 y código generado.</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 201 Created; código REP-2026-XXXX; estado PENDIENTE; puntosOtorgados = 0; TransactionLoaderModal desplegado y cerrado</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 201 Created; código emitido; estado PENDIENTE con 0 pts</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>Reporte en BD esperando triaje</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-01</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>RF-REP-01</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván (FrontEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-REP-03-01</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Rechazo de reporte sin coordenadas GPS o dirección &lt; 5 caracteres</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>HU-03 / RF-REP-03 · POST /api/denuncias</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Ciudadano autenticado</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>{"categoria":"BASURAL","latitud":null,"longitud":null,"direccion":"ab"}</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>1. Enviar reporte con GPS nulo y dirección corta.</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request; mensaje: 'Coordenadas GPS y dirección válidas son obligatorias.'</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request retornado con mensaje exacto</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>Reporte no creado</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-02</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>RF-REP-03</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván (FrontEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-REP-06-01</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Soft delete ciudadano (ocultarUsuario = true) preservando registro</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>HU-VEC01 / RF-REP-06 / RF-REP-07 · PATCH /api/denuncias/{id}/ocultar</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Reporte cerrado con puntos cobrados</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Petición de archivado por ciudadano titular</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>1. Ciudadano presiona archivar en Mis Reportes.</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; ocultarUsuario pasa a true; desaparece de app móvil; permanece intacto en panel municipal</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Archivado visual confirmado; registro físico preservado en BD</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>Historial municipal intacto</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-03</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>RF-REP-06</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván (FrontEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-ADM-01-01</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Triaje: Aprobación de reporte con prioridad ALTA e ingreso a bolsa</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>HU-05 / RF-ADM-01 · POST /api/denuncias/{id}/triaje</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Reporte PENDIENTE; token ADMIN</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>{"accion":"APROBAR","prioridad":"ALTA","observacionesAdmin":"Cercano a escuela provincial"}</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>1. Admin aprueba reporte asignando prioridad ALTA.</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; estado pasa a APROBADO; visible en bolsa de agentes con etiqueta ALTA (naranja)</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; caso visible en bolsa</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>Caso disponible para toma</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-04</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-01</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-ADM-02-01</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Triaje: Rechazo de reporte improcedente con justificación obligatoria</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>HU-05 / RF-ADM-02 · POST /api/denuncias/{id}/triaje</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Reporte PENDIENTE; token ADMIN</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>{"accion":"RECHAZAR","observacionesAdmin":"Foto borrosa de internet sin vía pública"}</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>1. Admin rechaza reporte con motivo.</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; estado pasa a RECHAZADO; puntos = 0; observacionesAdmin guardadas; notificación a vecino</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; caso rechazado y cerrado con 0 pts</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>Caso no ingresa a la bolsa</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-05</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-02</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-ADM-02-02</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Rechazo fallido si observacionesAdmin está vacío</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-02 · Validación en triaje</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Reporte PENDIENTE</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>{"accion":"RECHAZAR","observacionesAdmin":""}</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>1. Intentar rechazar con observaciones en blanco.</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request; mensaje: 'Debes ingresar el motivo del rechazo del reporte.'</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 400 devuelto con bloqueo de validación</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Estado se mantiene en PENDIENTE</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-06</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-02</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-ADM-03-01</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Bloqueo de asignación si inspector tiene disponible = false</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-03b · POST /api/denuncias/{id}/asignar</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Inspector con disponible = false</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>{"agenteId":"inspector-inactivo"}</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>1. Admin intenta asignar reporte a inspector inactivo.</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request; mensaje exacto: 'Agente no disponible'; banner rojo en UI</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 400 recibido y banner 'Agente no disponible' mostrado</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>Denuncia permanece en bolsa</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-07</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-03b</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AGE-02-01</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Toma de caso atómica 1 a 1 por agente pasando a EN_VERIFICACION</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>HU-08 / RF-AGE-02 · POST /api/denuncias/{id}/tomar</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Caso APROBADO; agente libre</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Agente presiona 'Tomar Caso'</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>1. Enviar solicitud de toma de caso.
-2. Validar asignación y bloqueo.</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; estado pasa a EN_VERIFICACION; agenteId asignado; caso desaparece de la bolsa común</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Caso tomado con estado EN_VERIFICACION</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>Agente tiene 1 caso activo</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-08</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>RF-AGE-02</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AGE-03-01</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Bloqueo de toma de nuevo caso si el agente ya tiene un caso activo</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>RF-AGE-03 · POST /api/denuncias/{id}/tomar</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Agente ya posee un caso EN_VERIFICACION</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Intento de tomar un segundo caso</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>1. Agente con caso asignado pulsa 'Tomar Caso' en otro incidente.</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request; mensaje: 'Ya tienes un caso activo asignado. Debes completarlo o liberarlo antes de tomar uno nuevo.'</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Bloqueo validado con mensaje de caso activo</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>Solo 1 caso por agente</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-09</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>RF-AGE-03</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AGE-05-01</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Verificación in situ Caso A: Foco real confirmado y foto contraprueba</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>HU-09 / RF-AGE-05 · POST /api/denuncias/{id}/verificar</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Caso asignado en EN_VERIFICACION</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>{"resultado":"REAL","fotoVerificacionUrl":"data:image...","notasInspeccion":"Basural real en vereda"}</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>1. Agente sube contraprueba y marca REAL.</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; estado pasa a VERIFICADO_PENDIENTE; pasa a bandeja de auditoría de Admin</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Estado actualizado a VERIFICADO_PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>Esperando acreditación de puntos</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-10</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>RF-AGE-05</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AGE-05-02</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Verificación in situ Caso B: Falso reporte en terreno</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>HU-09 / RF-AGE-05 · POST /api/denuncias/{id}/verificar</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Caso asignado en EN_VERIFICACION</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>{"resultado":"FALSO","fotoVerificacionUrl":"data:image...","notasInspeccion":"Terreno limpio sin residuos"}</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>1. Agente constata falsedad y sube descargo.</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; estado pasa a RECHAZADO; 0 puntos acreditados; agente liberado</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>Caso cerrado como falso con 0 pts</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>Caso finalizado</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-11</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>RF-AGE-05</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AGE-06-01</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Verificación in situ Caso C: Visita inaccesible e incremento de intentos</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>HU-09 / RF-AGE-06 · POST /api/denuncias/{id}/verificar</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Caso en EN_VERIFICACION con intentos = 0</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>{"resultado":"INACCESIBLE","fotoVerificacionUrl":"data:image_aviso...","notasInspeccion":"Portón con candado"}</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>1. Agente reporta inaccesibilidad y sube foto de sticker.</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; intentosInaccesible se incrementa a 1; caso retorna a bolsa como APROBADO</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Contador incrementado a 1 y caso retornado</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>Permite segunda visita</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-12</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>RF-AGE-06</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-ADM-04-01</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Acreditación atómica de puntos al ciudadano según baremo de prioridad</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-04 / RF-ADM-05 · POST /api/denuncias/{id}/acreditar-puntos</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Caso VERIFICADO_PENDIENTE prioridad ALTA; saldo vecino: 100</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>{"puntos":250,"observacionesAdmin":"Foco real confirmado"}</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>1. Admin acredita 250 puntos (rango ALTA: 200-300).</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; saldo vecino incrementa a 350 pts; puntosOtorgados = 250; estado pasa a EN_SANEAMIENTO; registro en PuntosHistory; notificación push enviada</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Transacción atómica exitosa; saldo final = 350 pts</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Puntos disponibles para tienda</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-13</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-04</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-ADM-04-02</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Rechazo de asignación de puntos fuera del baremo oficial</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-04 · Validación de baremo</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Caso prioridad BAJA (rango: 50 a 80 pts)</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>{"puntos":150}</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>1. Intentar asignar 150 pts a caso de prioridad BAJA.</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request; mensaje: 'El puntaje para prioridad BAJA debe estar comprendido entre 50 y 80 puntos.'; saldo del vecino inalterado</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 400 recibido; puntos bloqueados</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Saldo sin cambios</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-14</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-04</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AGE-07-01</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Liberación voluntaria de caso no verificado volviendo a APROBADO</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>HU-10 / RF-AGE-07 · POST /api/denuncias/{id}/liberar</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Caso EN_VERIFICACION sin validar</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Agente presiona 'Liberar Caso'</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>1. Agente libera caso por imprevisto.</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; agenteId pasa a null; estado retorna a APROBADO en bolsa común</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>Caso retornado a bolsa en estado APROBADO</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Disponible para otro inspector</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-15</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>RF-AGE-07</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P20" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AGE-08-01</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Saneamiento técnico: agente sube foto solución e informe técnico</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>HU-11 / RF-AGE-08 · POST /api/denuncias/{id}/sanear</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Caso EN_SANEAMIENTO asignado</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>{"fotoSolucionUrl":"data:image_despues...","informeSolucion":"Se retiraron 2 toneladas de residuos"}</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>1. Agente sube evidencia de limpieza.</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; estado pasa a RESUELTO_TECNICO; agente liberado para tomar otro caso; pasa a certificación de Admin</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Caso en RESUELTO_TECNICO; agente libre</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Esperando doble certificación</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-16</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>RF-AGE-08</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-ADM-07-01</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Doble certificación: Admin aprueba Antes vs Después a RESUELTO definitivo</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>HU-07 / RF-ADM-07 / RF-ADM-08 · POST /api/denuncias/{id}/certificar</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Caso en RESUELTO_TECNICO con ambas fotos</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>{"decision":"APROBADO"}</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>1. Admin compara fotos Antes y Después y certifica.</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; estado pasa a RESUELTO definitivo; fechaCierre registrada; notificación de cierre enviada al ciudadano</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Caso cerrado definitivamente en RESUELTO</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Ciclo de reporte completado</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-17</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-07</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P22" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-ADM-07-02</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Doble certificación: Admin observa limpieza y retorna a EN_SANEAMIENTO</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>HU-07 / RF-ADM-07 · POST /api/denuncias/{id}/certificar</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Caso en RESUELTO_TECNICO</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>{"decision":"OBSERVAR","observacionesAdmin":"Quedaron restos de escombros sobre la vereda"}</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>1. Admin rechaza limpieza con observaciones técnicas.</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 200 OK; estado retorna a EN_SANEAMIENTO; observacionesAdmin visibles para el inspector; reingresa a bolsa de saneamiento</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Caso devuelto a EN_SANEAMIENTO con observaciones</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Requiere nueva limpieza</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261025-18</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>RF-ADM-07</t>
-        </is>
-      </c>
-      <c r="N23" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-TIE-01-01</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>ABM catálogo: Carga y edición de producto con stock y precio en puntos</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>RF-TIE-01 · POST &amp; PUT /api/productos</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Token ADMIN</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>{"nombre":"Gorra Eco","categoria":"Indumentaria","puntos":150,"stock":20,"activo":true}</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>1. Crear producto.
-2. Modificar precio y stock.</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 201 en creación y 200 en edición; producto visible en catálogo con nuevos valores</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Producto creado y actualizado en catálogo</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Catálogo actualizado</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261026-01</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>RF-TIE-01</t>
-        </is>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P24" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-TIE-05-04</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Confirmación atómica de canje y emisión de código de retiro</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>HU-08 / RF-TIE-05 · POST /api/canjes/confirmar</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Reserva activa; sucursal seleccionada</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>{"reservaId":"res-1","sucursalId":"suc-pilar-centro"}</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>1. Confirmar canje presencial.</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 201 Created; deducción atómica de puntos y stock definitivo; carrito vaciado; emisión de codigoRetiro único (ej. ECO-7142-N); fechaExpiracion = now + 30 días; comprobante generado</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>HTTP 201 Created; código ECO-7142-N emitido</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Canje confirmado para retiro</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261026-03</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>RF-TIE-05</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-COL-01-01</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Búsqueda de código y confirmación de entrega presencial por colaborador</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>RF-COL-01 · POST /api/canjes/{codigo}/entregar</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Pedido CONFIRMADO; token COLLABORATOR</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>{"codigoRetiro":"ECO-7142-N"}</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>1. Colaborador busca código.
-2. Valida titular.
-3. Presiona Confirmar Entrega.</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Al buscar: datos del titular y productos desplegados; al confirmar: HTTP 200 OK, estado pasa a ENTREGADO, fechaEntrega = now, entregadoPor = collaboratorId; banner verde de éxito</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Entrega confirmada y pedido cerrado exitosamente</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>Código inhabilitado para futuras entregas</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261026-04</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>RF-COL-01</t>
-        </is>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P26" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-COL-01-02</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Alertas ante código de retiro inexistente o ya entregado</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>RF-COL-01 · GET /api/canjes/{codigo}</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Código erróneo o canje ENTREGADO</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Buscar 'ECO-0000-X' y luego 'ECO-YA-ENTREGADO'</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>1. Buscar código inexistente.
-2. Buscar código ya entregado.</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Caso 1: Banner rojo: 'El código de retiro no existe. Por favor, verifica los caracteres con el vecino.'; Caso 2: Banner amarillo: 'Este canje ya fue retirado el día [Fecha] a las [Hora].'</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Banners con textos exactos mostrados</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>Previene doble entrega</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>LOG-API-20261026-05</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>RF-COL-01</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>API / Funcional</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>CP-RNF-07-01</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Seguridad RBAC: Rechazo 401 y 403 ante llamadas no autorizadas</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>RNF-07 · Seguridad de endpoints</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>Endpoints protegidos /api/denuncias/{id}/triaje y /api/productos</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Invocación sin token y luego con token de rol CITIZEN</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>1. Llamar endpoint sin token.
-2. Llamar con token Citizen.</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Sin token: HTTP 401 Unauthorized; Con token Citizen: HTTP 403 Forbidden: 'Acceso denegado: se requieren privilegios de Administrador'</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>401 y 403 devueltos exactamente</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>Endpoints protegidos</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>SEC-RBAC-AUDIT-01</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>RNF-07</t>
-        </is>
-      </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>Postman</t>
-        </is>
-      </c>
-      <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="P28" s="4" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="37" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="33" customWidth="1" min="17" max="17"/>
@@ -10479,12 +8151,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>CP-RF-REP-04-01</t>
+          <t>CP-RF-AUT-01-01</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Verificación de estado inicial PENDIENTE y 0 ecopuntos en reporte</t>
+          <t>Flujo nominal — Registro del ciudadano con rol CITIZEN y balance 0</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10494,32 +8166,34 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>RF-REP-04 · Integridad en Base de Datos</t>
+          <t>RF-AUT-01 · POST /api/auth/register</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Reporte recién insertado</t>
+          <t>BD limpia; correo sin registrar</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Consulta SQL/Prisma a tabla Denuncia</t>
+          <t>{"nombre":"Carlos Alberto Gómez","email":"ciudadano.valido@ecoalerta.gob.ar","password":"PasswordEco2026!"}</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1. Consultar registro por ID.</t>
+          <t>1. Enviar POST /api/auth/register con payload válido.
+2. Validar HTTP status.
+3. Validar rol y puntos en BD.</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>estado = 'PENDIENTE', puntosOtorgados = 0, agenteId = null</t>
+          <t>HTTP 201 Created; token JWT emitido; user.rol='CITIZEN', puntos=0; redirección a CitizenHomeScreen</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Campos verificados en BD</t>
+          <t>HTTP 201 Created; token válido; rol CITIZEN asignado con 0 puntos</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -10529,27 +8203,27 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Denuncia a la espera de triaje</t>
+          <t>Usuario persistido en BD</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>TEST-DB-STATUS-01</t>
+          <t>LOG-API-20261024-01</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>RF-REP-04</t>
+          <t>RF-AUT-01</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Postman</t>
         </is>
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>Unitario / Integración</t>
+          <t>API / Funcional</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
@@ -10559,54 +8233,55 @@
       </c>
       <c r="Q2" s="4" t="inlineStr">
         <is>
-          <t>Rodriguez Iván (FrontEnd)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>CP-RF-AGE-02-02</t>
+          <t>CP-RF-AUT-01-02</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Concurrencia: Intento simultáneo de toma del mismo caso por 2 inspectores</t>
+          <t>Rechazo de registro ante correo electrónico duplicado</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>HU-08 / RF-AGE-02 / RNF-03 · Concurrencia Prisma</t>
+          <t>RF-AUT-02 · POST /api/auth/register</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Caso APROBADO; 2 agentes libres</t>
+          <t>Usuario ya registrado con correo vecino.registrado@pilar.gob.ar</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2 llamadas simultáneas a /api/denuncias/{id}/tomar con Promise.all()</t>
+          <t>{"nombre":"Esteban Quito","email":"vecino.registrado@pilar.gob.ar","password":"ClaveSegura123!"}</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>1. Disparar dos peticiones concurrentes en el ms 0.</t>
+          <t>1. Enviar POST /api/auth/register con correo ya existente.
+2. Validar respuesta de error.</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>1 petición retorna 200 OK (caso asignado); la otra retorna 409 Conflict con mensaje: 'El caso ya ha sido tomado por otro inspector.'; cero doble asignación</t>
+          <t>HTTP 409 Conflict; mensaje: 'El correo electrónico ya se encuentra registrado.'</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>1 asignación exitosa, 1 rechazo 409 controlado; cero condiciones de carrera</t>
+          <t>HTTP 409 Conflict recibido con mensaje exacto</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -10616,27 +8291,27 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Exactamente un agente asignado</t>
+          <t>No se crea registro duplicado</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>CONC-TOMA-CASO-01</t>
+          <t>LOG-API-20261024-02</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>RF-AGE-02</t>
+          <t>RF-AUT-02</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Postman</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>Concurrencia / Resiliencia</t>
+          <t>API / Funcional</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
@@ -10646,19 +8321,19 @@
       </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
-          <t>Benitez Angel (BackEnd)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>CP-RF-AGE-06-02</t>
+          <t>CP-RF-AUT-03-01</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Protocolo de 3 intentos: Cierre a CERRADO_INACCESIBLE al 3.er fallo</t>
+          <t>Login exitoso con credenciales válidas y emisión de JWT</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -10668,32 +8343,33 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>HU-09 / RF-AGE-06 · Regla de 3 visitas</t>
+          <t>RF-AUT-03 · POST /api/auth/login</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Caso con intentosInaccesible = 2</t>
+          <t>Usuario maria.agente@pilar.gob.ar activo con rol AGENT</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>{"resultado":"INACCESIBLE","fotoVerificacionUrl":"data:image_aviso3...","notasInspeccion":"3ra visita sin acceso"}</t>
+          <t>{"identifier":"maria.agente@pilar.gob.ar","password":"ClaveAgente1!"}</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>1. Registrar tercera visita fallida.</t>
+          <t>1. Enviar POST /api/auth/login con credenciales válidas.
+2. Validar JWT y datos de usuario.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 OK; intentosInaccesible = 3; estado cambia automáticamente a CERRADO_INACCESIBLE; agente liberado; derivación legal sin penalizar a vecino</t>
+          <t>HTTP 200 OK; token JWT firmado retornado; payload incluye {id, rol:'AGENT'}</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Cierre automático en 3.er fallo verificado</t>
+          <t>HTTP 200 OK; token emitido correctamente</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -10703,27 +8379,27 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Caso derivado a legales</t>
+          <t>Token almacenado en cliente</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>TEST-3-INTENTOS-01</t>
+          <t>LOG-API-20261024-03</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>RF-AGE-06</t>
+          <t>RF-AUT-03</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Postman</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>Unitario / Integración</t>
+          <t>API / Funcional</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
@@ -10733,19 +8409,19 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Benitez Angel (BackEnd)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>CP-RF-AGE-07-02</t>
+          <t>CP-RF-AUT-03-02</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Liberación de caso verificado: retorna a bolsa como EN_SANEAMIENTO</t>
+          <t>Login fallido por contraseña errónea</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -10755,32 +8431,32 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>HU-10 / RF-AGE-07 · Regla de reasignación</t>
+          <t>RF-AUT-03 · POST /api/auth/login</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Caso EN_SANEAMIENTO con puntos ya otorgados</t>
+          <t>Usuario admin@pilar.gob.ar existente</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Agente o Admin fuerzan liberación</t>
+          <t>{"identifier":"admin@pilar.gob.ar","password":"ClaveEquivocada999"}</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>1. Liberar caso verificado.</t>
+          <t>1. Enviar POST /api/auth/login con contraseña inválida.</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 OK; agenteId pasa a null; estado retorna como EN_SANEAMIENTO (no a APROBADO); nuevo agente salta directo a saneamiento</t>
+          <t>HTTP 401 Unauthorized; mensaje: 'Credenciales inválidas'; banner rojo en UI: 'El correo electrónico o la contraseña son incorrectos. Por favor, verifica tus datos.'</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Retorno como EN_SANEAMIENTO confirmado</t>
+          <t>HTTP 401 recibido y banner rojo desplegado</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -10790,49 +8466,49 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Preserva verificación previa</t>
+          <t>Sesión no iniciada</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>TEST-REASIGN-01</t>
+          <t>LOG-API-20261024-04</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>RF-AGE-07</t>
+          <t>RF-AUT-03</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Postman</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>Unitario / Integración</t>
+          <t>API / Funcional</t>
         </is>
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Negativo</t>
         </is>
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>Benitez Angel (BackEnd)</t>
+          <t>Rodriguez Iván / Benitez Angel</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>CP-RF-TIE-01-02</t>
+          <t>CP-RF-REP-01-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Baja lógica de producto (activo = false) preservando historial de canjes</t>
+          <t>Creación exitosa de reporte ciudadano con GPS y foto comprimida</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -10842,32 +8518,33 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>RF-TIE-01 · DELETE /api/productos/{id}</t>
+          <t>HU-03 / RF-REP-01 / RF-REP-04 · POST /api/denuncias</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Producto con canjes previos asociados en OrderItem</t>
+          <t>Ciudadano autenticado con token válido</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Admin presiona eliminar producto</t>
+          <t>{"categoria":"BASURAL","descripcion":"Microbasural clandestino","latitud":-34.4586,"longitud":-58.9142,"direccion":"Las Palmeras 1230","fotoUrl":"data:image/jpeg..."}</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>1. Enviar DELETE /api/productos/{id}.</t>
+          <t>1. Enviar reporte con datos completos.
+2. Validar HTTP 201 y código generado.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>HTTP 200 OK; registro físico preservado (sin error de FK); activo pasa a false; producto no visible en tienda; histórico de compras intacto</t>
+          <t>HTTP 201 Created; código REP-2026-XXXX; estado PENDIENTE; puntosOtorgados = 0; TransactionLoaderModal desplegado y cerrado</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Baja lógica confirmada; cero errores de FK</t>
+          <t>HTTP 201 Created; código emitido; estado PENDIENTE con 0 pts</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -10877,27 +8554,27 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Integridad referencial intacta</t>
+          <t>Reporte en BD esperando triaje</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>TEST-BAJA-LOGICA-01</t>
+          <t>LOG-API-20261025-01</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>RF-TIE-01</t>
+          <t>RF-REP-01</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Postman</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>Unitario / Integración</t>
+          <t>API / Funcional</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
@@ -10907,19 +8584,19 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>CP-RF-TIE-04-02</t>
+          <t>CP-RF-REP-03-01</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Revalidación atómica de precio en BD al abrir Checkout</t>
+          <t>Rechazo de reporte sin coordenadas GPS o dirección &lt; 5 caracteres</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -10929,32 +8606,32 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>RF-TIE-04 · POST /api/canjes/checkout-init</t>
+          <t>HU-03 / RF-REP-03 · POST /api/denuncias</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Producto en carrito a 100 pts modificado a 120 pts por Admin</t>
+          <t>Ciudadano autenticado</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Iniciar checkout</t>
+          <t>{"categoria":"BASURAL","latitud":null,"longitud":null,"direccion":"ab"}</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>1. Backend revalida precios contra tabla Product.</t>
+          <t>1. Enviar reporte con GPS nulo y dirección corta.</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Detecta cambio de precio; actualiza total en pantalla y notifica al usuario del nuevo valor</t>
+          <t>HTTP 400 Bad Request; mensaje: 'Coordenadas GPS y dirección válidas son obligatorias.'</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Revalidación de precio ejecutada con éxito</t>
+          <t>HTTP 400 Bad Request retornado con mensaje exacto</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -10964,84 +8641,84 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Evita cobro con precios desfasados</t>
+          <t>Reporte no creado</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>TEST-REVALIDA-01</t>
+          <t>LOG-API-20261025-02</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>RF-TIE-04</t>
+          <t>RF-REP-03</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Postman</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>Unitario / Integración</t>
+          <t>API / Funcional</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Negativo</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>CP-RF-TIE-05-02</t>
+          <t>CP-RF-REP-04-01</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Concurrencia: Intento simultáneo de reserva de última unidad de stock</t>
+          <t>Verificación de estado inicial PENDIENTE y 0 ecopuntos en reporte</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>HU-08 / RF-TIE-05 / RNF-03 · Concurrencia Prisma</t>
+          <t>RF-REP-04 · Integridad en Base de Datos</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Producto con stock = 1; 2 ciudadanos intentan reservar al mismo tiempo</t>
+          <t>Reporte recién insertado</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Llamadas concurrentes con Promise.all()</t>
+          <t>Consulta SQL/Prisma a tabla Denuncia</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>1. Disparar reservas paralelas de la última unidad.</t>
+          <t>1. Consultar registro por ID.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>1 solicitud recibe 200 OK (reserva concedida); la otra recibe 409 Conflict: 'Stock insuficiente. El producto acaba de ser reservado por otro usuario.'; stock final = 0</t>
+          <t>estado = 'PENDIENTE', puntosOtorgados = 0, agenteId = null</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>1 éxito, 1 conflicto 409; cero sobreventa (tras fix atómico en BUG-102)</t>
+          <t>Campos verificados en BD</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -11051,122 +8728,2477 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Stock nunca inferior a 0</t>
+          <t>Denuncia a la espera de triaje</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>CONC-CHECKOUT-01</t>
+          <t>TEST-DB-STATUS-01</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>RF-TIE-05</t>
+          <t>RF-REP-04</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>Concurrencia / Resiliencia</t>
+          <t>Unitario / Integración</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>Negativo</t>
+          <t>Positivo</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
+          <t>Rodriguez Iván (FrontEnd)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>CP-RF-REP-06-01</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Soft delete ciudadano (ocultarUsuario = true) preservando registro</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>HU-VEC01 / RF-REP-06 / RF-REP-07 · PATCH /api/denuncias/{id}/ocultar</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Reporte cerrado con puntos cobrados</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Petición de archivado por ciudadano titular</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>1. Ciudadano presiona archivar en Mis Reportes.</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; ocultarUsuario pasa a true; desaparece de app móvil; permanece intacto en panel municipal</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Archivado visual confirmado; registro físico preservado en BD</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Historial municipal intacto</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-03</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>RF-REP-06</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván (FrontEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-ADM-01-01</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Triaje: Aprobación de reporte con prioridad ALTA e ingreso a bolsa</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>HU-05 / RF-ADM-01 · POST /api/denuncias/{id}/triaje</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Reporte PENDIENTE; token ADMIN</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>{"accion":"APROBAR","prioridad":"ALTA","observacionesAdmin":"Cercano a escuela provincial"}</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>1. Admin aprueba reporte asignando prioridad ALTA.</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; estado pasa a APROBADO; visible en bolsa de agentes con etiqueta ALTA (naranja)</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; caso visible en bolsa</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Caso disponible para toma</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-04</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-01</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-ADM-02-01</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Triaje: Rechazo de reporte improcedente con justificación obligatoria</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>HU-05 / RF-ADM-02 · POST /api/denuncias/{id}/triaje</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Reporte PENDIENTE; token ADMIN</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>{"accion":"RECHAZAR","observacionesAdmin":"Foto borrosa de internet sin vía pública"}</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>1. Admin rechaza reporte con motivo.</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; estado pasa a RECHAZADO; puntos = 0; observacionesAdmin guardadas; notificación a vecino</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; caso rechazado y cerrado con 0 pts</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Caso no ingresa a la bolsa</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-05</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-02</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-ADM-02-02</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Rechazo fallido si observacionesAdmin está vacío</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-02 · Validación en triaje</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Reporte PENDIENTE</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>{"accion":"RECHAZAR","observacionesAdmin":""}</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>1. Intentar rechazar con observaciones en blanco.</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request; mensaje: 'Debes ingresar el motivo del rechazo del reporte.'</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 400 devuelto con bloqueo de validación</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Estado se mantiene en PENDIENTE</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-06</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-02</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-ADM-03-01</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Bloqueo de asignación si inspector tiene disponible = false</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-03b · POST /api/denuncias/{id}/asignar</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Inspector con disponible = false</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>{"agenteId":"inspector-inactivo"}</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>1. Admin intenta asignar reporte a inspector inactivo.</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request; mensaje exacto: 'Agente no disponible'; banner rojo en UI</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 400 recibido y banner 'Agente no disponible' mostrado</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Denuncia permanece en bolsa</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-07</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-03b</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AGE-02-01</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Toma de caso atómica 1 a 1 por agente pasando a EN_VERIFICACION</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>HU-08 / RF-AGE-02 · POST /api/denuncias/{id}/tomar</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Caso APROBADO; agente libre</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Agente presiona 'Tomar Caso'</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>1. Enviar solicitud de toma de caso.
+2. Validar asignación y bloqueo.</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; estado pasa a EN_VERIFICACION; agenteId asignado; caso desaparece de la bolsa común</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Caso tomado con estado EN_VERIFICACION</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Agente tiene 1 caso activo</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-08</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-02</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AGE-02-02</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Concurrencia: Intento simultáneo de toma del mismo caso por 2 inspectores</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>HU-08 / RF-AGE-02 / RNF-03 · Concurrencia Prisma</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Caso APROBADO; 2 agentes libres</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>2 llamadas simultáneas a /api/denuncias/{id}/tomar con Promise.all()</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>1. Disparar dos peticiones concurrentes en el ms 0.</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>1 petición retorna 200 OK (caso asignado); la otra retorna 409 Conflict con mensaje: 'El caso ya ha sido tomado por otro inspector.'; cero doble asignación</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>1 asignación exitosa, 1 rechazo 409 controlado; cero condiciones de carrera</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Exactamente un agente asignado</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>CONC-TOMA-CASO-01</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-02</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Supertest / NodeRunner</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>Concurrencia / Resiliencia</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AGE-03-01</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Bloqueo de toma de nuevo caso si el agente ya tiene un caso activo</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-03 · POST /api/denuncias/{id}/tomar</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Agente ya posee un caso EN_VERIFICACION</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Intento de tomar un segundo caso</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>1. Agente con caso asignado pulsa 'Tomar Caso' en otro incidente.</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request; mensaje: 'Ya tienes un caso activo asignado. Debes completarlo o liberarlo antes de tomar uno nuevo.'</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Bloqueo validado con mensaje de caso activo</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Solo 1 caso por agente</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-09</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-03</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AGE-05-01</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Verificación in situ Caso A: Foco real confirmado y foto contraprueba</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>HU-09 / RF-AGE-05 · POST /api/denuncias/{id}/verificar</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Caso asignado en EN_VERIFICACION</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>{"resultado":"REAL","fotoVerificacionUrl":"data:image...","notasInspeccion":"Basural real en vereda"}</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>1. Agente sube contraprueba y marca REAL.</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; estado pasa a VERIFICADO_PENDIENTE; pasa a bandeja de auditoría de Admin</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Estado actualizado a VERIFICADO_PENDIENTE</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Esperando acreditación de puntos</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-10</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-05</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AGE-05-02</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Verificación in situ Caso B: Falso reporte en terreno</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>HU-09 / RF-AGE-05 · POST /api/denuncias/{id}/verificar</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Caso asignado en EN_VERIFICACION</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>{"resultado":"FALSO","fotoVerificacionUrl":"data:image...","notasInspeccion":"Terreno limpio sin residuos"}</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>1. Agente constata falsedad y sube descargo.</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; estado pasa a RECHAZADO; 0 puntos acreditados; agente liberado</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Caso cerrado como falso con 0 pts</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Caso finalizado</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-11</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-05</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AGE-06-01</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Verificación in situ Caso C: Visita inaccesible e incremento de intentos</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>HU-09 / RF-AGE-06 · POST /api/denuncias/{id}/verificar</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Caso en EN_VERIFICACION con intentos = 0</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>{"resultado":"INACCESIBLE","fotoVerificacionUrl":"data:image_aviso...","notasInspeccion":"Portón con candado"}</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>1. Agente reporta inaccesibilidad y sube foto de sticker.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; intentosInaccesible se incrementa a 1; caso retorna a bolsa como APROBADO</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Contador incrementado a 1 y caso retornado</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Permite segunda visita</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-12</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-06</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AGE-06-02</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Protocolo de 3 intentos: Cierre a CERRADO_INACCESIBLE al 3.er fallo</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>HU-09 / RF-AGE-06 · Regla de 3 visitas</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Caso con intentosInaccesible = 2</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>{"resultado":"INACCESIBLE","fotoVerificacionUrl":"data:image_aviso3...","notasInspeccion":"3ra visita sin acceso"}</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>1. Registrar tercera visita fallida.</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; intentosInaccesible = 3; estado cambia automáticamente a CERRADO_INACCESIBLE; agente liberado; derivación legal sin penalizar a vecino</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Cierre automático en 3.er fallo verificado</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Caso derivado a legales</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>TEST-3-INTENTOS-01</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-06</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Supertest / NodeRunner</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>Unitario / Integración</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-ADM-04-01</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Acreditación atómica de puntos al ciudadano según baremo de prioridad</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-04 / RF-ADM-05 · POST /api/denuncias/{id}/acreditar-puntos</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Caso VERIFICADO_PENDIENTE prioridad ALTA; saldo vecino: 100</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>{"puntos":250,"observacionesAdmin":"Foco real confirmado"}</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>1. Admin acredita 250 puntos (rango ALTA: 200-300).</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; saldo vecino incrementa a 350 pts; puntosOtorgados = 250; estado pasa a EN_SANEAMIENTO; registro en PuntosHistory; notificación push enviada</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Transacción atómica exitosa; saldo final = 350 pts</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Puntos disponibles para tienda</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-13</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-04</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-ADM-04-02</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Rechazo de asignación de puntos fuera del baremo oficial</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-04 · Validación de baremo</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Caso prioridad BAJA (rango: 50 a 80 pts)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>{"puntos":150}</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>1. Intentar asignar 150 pts a caso de prioridad BAJA.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request; mensaje: 'El puntaje para prioridad BAJA debe estar comprendido entre 50 y 80 puntos.'; saldo del vecino inalterado</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 400 recibido; puntos bloqueados</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Saldo sin cambios</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-14</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-04</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AGE-07-01</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Liberación voluntaria de caso no verificado volviendo a APROBADO</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>HU-10 / RF-AGE-07 · POST /api/denuncias/{id}/liberar</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Caso EN_VERIFICACION sin validar</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Agente presiona 'Liberar Caso'</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>1. Agente libera caso por imprevisto.</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; agenteId pasa a null; estado retorna a APROBADO en bolsa común</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Caso retornado a bolsa en estado APROBADO</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Disponible para otro inspector</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-15</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-07</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AGE-07-02</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Liberación de caso verificado: retorna a bolsa como EN_SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>HU-10 / RF-AGE-07 · Regla de reasignación</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Caso EN_SANEAMIENTO con puntos ya otorgados</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Agente o Admin fuerzan liberación</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>1. Liberar caso verificado.</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; agenteId pasa a null; estado retorna como EN_SANEAMIENTO (no a APROBADO); nuevo agente salta directo a saneamiento</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Retorno como EN_SANEAMIENTO confirmado</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Preserva verificación previa</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>TEST-REASIGN-01</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-07</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Supertest / NodeRunner</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>Unitario / Integración</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-AGE-08-01</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Saneamiento técnico: agente sube foto solución e informe técnico</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>HU-11 / RF-AGE-08 · POST /api/denuncias/{id}/sanear</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Caso EN_SANEAMIENTO asignado</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>{"fotoSolucionUrl":"data:image_despues...","informeSolucion":"Se retiraron 2 toneladas de residuos"}</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>1. Agente sube evidencia de limpieza.</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; estado pasa a RESUELTO_TECNICO; agente liberado para tomar otro caso; pasa a certificación de Admin</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Caso en RESUELTO_TECNICO; agente libre</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Esperando doble certificación</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-16</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>RF-AGE-08</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-ADM-07-01</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Doble certificación: Admin aprueba Antes vs Después a RESUELTO definitivo</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>HU-07 / RF-ADM-07 / RF-ADM-08 · POST /api/denuncias/{id}/certificar</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Caso en RESUELTO_TECNICO con ambas fotos</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>{"decision":"APROBADO"}</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>1. Admin compara fotos Antes y Después y certifica.</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; estado pasa a RESUELTO definitivo; fechaCierre registrada; notificación de cierre enviada al ciudadano</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Caso cerrado definitivamente en RESUELTO</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Ciclo de reporte completado</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-17</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-07</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-ADM-07-02</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Doble certificación: Admin observa limpieza y retorna a EN_SANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>HU-07 / RF-ADM-07 · POST /api/denuncias/{id}/certificar</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Caso en RESUELTO_TECNICO</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>{"decision":"OBSERVAR","observacionesAdmin":"Quedaron restos de escombros sobre la vereda"}</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>1. Admin rechaza limpieza con observaciones técnicas.</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; estado retorna a EN_SANEAMIENTO; observacionesAdmin visibles para el inspector; reingresa a bolsa de saneamiento</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Caso devuelto a EN_SANEAMIENTO con observaciones</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Requiere nueva limpieza</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261025-18</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>RF-ADM-07</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>Benitez Angel (BackEnd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-TIE-01-01</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>ABM catálogo: Carga y edición de producto con stock y precio en puntos</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>RF-TIE-01 · POST &amp; PUT /api/productos</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Token ADMIN</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>{"nombre":"Gorra Eco","categoria":"Indumentaria","puntos":150,"stock":20,"activo":true}</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>1. Crear producto.
+2. Modificar precio y stock.</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 201 en creación y 200 en edición; producto visible en catálogo con nuevos valores</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Producto creado y actualizado en catálogo</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Catálogo actualizado</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261026-01</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>RF-TIE-01</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-TIE-01-02</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Baja lógica de producto (activo = false) preservando historial de canjes</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>RF-TIE-01 · DELETE /api/productos/{id}</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Producto con canjes previos asociados en OrderItem</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Admin presiona eliminar producto</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>1. Enviar DELETE /api/productos/{id}.</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 200 OK; registro físico preservado (sin error de FK); activo pasa a false; producto no visible en tienda; histórico de compras intacto</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Baja lógica confirmada; cero errores de FK</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Integridad referencial intacta</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>TEST-BAJA-LOGICA-01</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>RF-TIE-01</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>Supertest / NodeRunner</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>Unitario / Integración</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-TIE-04-02</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Revalidación atómica de precio en BD al abrir Checkout</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>RF-TIE-04 · POST /api/canjes/checkout-init</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Producto en carrito a 100 pts modificado a 120 pts por Admin</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Iniciar checkout</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>1. Backend revalida precios contra tabla Product.</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Detecta cambio de precio; actualiza total en pantalla y notifica al usuario del nuevo valor</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Revalidación de precio ejecutada con éxito</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Evita cobro con precios desfasados</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>TEST-REVALIDA-01</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>RF-TIE-04</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>Supertest / NodeRunner</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>Unitario / Integración</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-TIE-05-02</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Concurrencia: Intento simultáneo de reserva de última unidad de stock</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>HU-08 / RF-TIE-05 / RNF-03 · Concurrencia Prisma</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Producto con stock = 1; 2 ciudadanos intentan reservar al mismo tiempo</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Llamadas concurrentes con Promise.all()</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>1. Disparar reservas paralelas de la última unidad.</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>1 solicitud recibe 200 OK (reserva concedida); la otra recibe 409 Conflict: 'Stock insuficiente. El producto acaba de ser reservado por otro usuario.'; stock final = 0</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>1 éxito, 1 conflicto 409; cero sobreventa (tras fix atómico en BUG-102)</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Stock nunca inferior a 0</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>CONC-CHECKOUT-01</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>RF-TIE-05</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>Supertest / NodeRunner</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>Concurrencia / Resiliencia</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-TIE-05-04</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Confirmación atómica de canje y emisión de código de retiro</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>HU-08 / RF-TIE-05 · POST /api/canjes/confirmar</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Reserva activa; sucursal seleccionada</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>{"reservaId":"res-1","sucursalId":"suc-pilar-centro"}</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>1. Confirmar canje presencial.</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 201 Created; deducción atómica de puntos y stock definitivo; carrito vaciado; emisión de codigoRetiro único (ej. ECO-7142-N); fechaExpiracion = now + 30 días; comprobante generado</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>HTTP 201 Created; código ECO-7142-N emitido</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Canje confirmado para retiro</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261026-03</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>RF-TIE-05</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-COL-01-01</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Búsqueda de código y confirmación de entrega presencial por colaborador</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>RF-COL-01 · POST /api/canjes/{codigo}/entregar</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Pedido CONFIRMADO; token COLLABORATOR</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>{"codigoRetiro":"ECO-7142-N"}</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>1. Colaborador busca código.
+2. Valida titular.
+3. Presiona Confirmar Entrega.</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Al buscar: datos del titular y productos desplegados; al confirmar: HTTP 200 OK, estado pasa a ENTREGADO, fechaEntrega = now, entregadoPor = collaboratorId; banner verde de éxito</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Entrega confirmada y pedido cerrado exitosamente</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>Código inhabilitado para futuras entregas</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261026-04</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>RF-COL-01</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CP-RF-COL-01-02</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Alertas ante código de retiro inexistente o ya entregado</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>RF-COL-01 · GET /api/canjes/{codigo}</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Código erróneo o canje ENTREGADO</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Buscar 'ECO-0000-X' y luego 'ECO-YA-ENTREGADO'</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>1. Buscar código inexistente.
+2. Buscar código ya entregado.</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Caso 1: Banner rojo: 'El código de retiro no existe. Por favor, verifica los caracteres con el vecino.'; Caso 2: Banner amarillo: 'Este canje ya fue retirado el día [Fecha] a las [Hora].'</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Banners con textos exactos mostrados</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Previene doble entrega</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>LOG-API-20261026-05</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>RF-COL-01</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>API / Funcional</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>CP-RF-TIE-06-01</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Expiración de canje tras 30 días sin retiro (reintegro sin reembolso)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>RF-TIE-06 · processCanjeExpirations()</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Canje CONFIRMADO con más de 30 días corridos de antigüedad</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Ejecución de job batch de expiración</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>1. Ejecutar worker sobre canjes vencidos.</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>Estado pasa a EXPIRADO; unidades de stock vuelven al catálogo disponible; puntos NO se reembolsan a la cuenta del ciudadano</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Stock reintegrado y puntos retenidos según directiva</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>Canje cerrado por caducidad</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>TEST-BATCH-EXPIRE-01</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>RF-TIE-06</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>Pytest</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>Supertest / NodeRunner</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>Unitario / Integración</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>Positivo</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>Rodriguez Iván / Benitez Angel</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>CP-RNF-07-01</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Seguridad RBAC: Rechazo 401 y 403 ante llamadas no autorizadas</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>RNF-07 · Seguridad de endpoints</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Endpoints protegidos /api/denuncias/{id}/triaje y /api/productos</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Invocación sin token y luego con token de rol CITIZEN</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>1. Llamar endpoint sin token.
+2. Llamar con token Citizen.</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Sin token: HTTP 401 Unauthorized; Con token Citizen: HTTP 403 Forbidden: 'Acceso denegado: se requieren privilegios de Administrador'</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>401 y 403 devueltos exactamente</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Pasó</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>Endpoints protegidos</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>SEC-RBAC-AUDIT-01</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>RNF-07</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>Rodriguez Iván / Benitez Angel</t>
         </is>
@@ -11177,479 +11209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
-    <col width="49" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="47" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="33" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>ID del Caso</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>Prioridad</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>Funcionalidad a testar</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>Precondiciones</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>Datos de prueba</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
-        <is>
-          <t>Pasos a ejecutar</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>Resultado esperado</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>Resultado Real</t>
-        </is>
-      </c>
-      <c r="J1" s="10" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="K1" s="10" t="inlineStr">
-        <is>
-          <t>Postcondiciones</t>
-        </is>
-      </c>
-      <c r="L1" s="10" t="inlineStr">
-        <is>
-          <t>Evidencia</t>
-        </is>
-      </c>
-      <c r="M1" s="10" t="inlineStr">
-        <is>
-          <t>ID Requerimiento</t>
-        </is>
-      </c>
-      <c r="N1" s="10" t="inlineStr">
-        <is>
-          <t>Herramienta</t>
-        </is>
-      </c>
-      <c r="O1" s="10" t="inlineStr">
-        <is>
-          <t>Tipo de prueba</t>
-        </is>
-      </c>
-      <c r="P1" s="10" t="inlineStr">
-        <is>
-          <t>Escenario</t>
-        </is>
-      </c>
-      <c r="Q1" s="10" t="inlineStr">
-        <is>
-          <t>Responsable Corrección Bug</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AUT-04-01</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Enrutamiento dinámico según rol (CITIZEN, AGENT, ADMIN, COLLABORATOR)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-04 · Navegación React Navigation</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>4 usuarios de prueba con cada uno de los roles</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Tokens válidos para cada rol</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>1. Iniciar sesión con cada rol.
-2. Validar pantalla inicial de aterrizaje.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>CITIZEN -&gt; CitizenHomeScreen, AGENT -&gt; AgentHomeScreen, ADMIN -&gt; AdminDenunciasScreen, COLLABORATOR -&gt; CollaboratorDeliveryScreen</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Navegación determinista según rol verificada</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>Entorno cargado según perfil</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>E2E-NAV-ROLES-01</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-04</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>Cypress</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
-        <is>
-          <t>UI / E2E</t>
-        </is>
-      </c>
-      <c r="P2" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q2" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AUT-06-02</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Botón CTA de cabecera 'Regístrate para empezar a usar la app'</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>HU-INV-02 / RF-AUT-06 · Header Component</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Usuario en Modo Invitado en Home</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Clic en botón de cabecera</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>1. Verificar texto de botón.
-2. Presionar botón.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Botón verde con texto exacto; navega a RegisterScreen en &lt; 150 ms</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Texto verificado y navegación fluida</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Pantalla de registro montada</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>UI-CTA-HEADER-01</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>HU-INV-02</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>Cypress</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>UI / E2E</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AUT-07-01</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Navegación libre en Modo Invitado solo lectura en Tienda</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>HU-INV-03 / RF-AUT-07 · StoreScreen</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Usuario en Modo Invitado</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Navegar a pestaña Tienda</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>1. Abrir Tienda.
-2. Filtrar por categorías y buscar producto.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Muestra catálogo de productos con precios en puntos; buscador funciona en lectura; no muestra botón de checkout</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Catálogo explorable en modo lectura</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>Estado de invitado preservado</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>UI-GUEST-STORE-01</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>RF-AUT-07</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Cypress</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>UI / E2E</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>Rodriguez Iván / Benitez Angel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>CP-RF-AGE-01-01</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Visualización de casos en bolsa con semáforo de prioridad</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>HU-08 / RF-AGE-01 · AgentHomeScreen</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Agente autenticado en servicio</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Abrir bandeja de casos aprobados</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>1. Cargar bolsa de casos.
-2. Validar orden y colores.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Casos ordenados por severidad; Rojo (Urgente), Naranja (Alta), Amarillo (Media), Verde (Baja); muestra distancia GPS</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Bolsa renderizada con semáforos correctos</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Pasó</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>Agente informado de prioridades</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>UI-BOLSA-CASOS-01</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>RF-AGE-01</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>Cypress</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>UI / E2E</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>Benitez Angel (BackEnd)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11665,7 +11225,7 @@
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="33" customWidth="1" min="10" max="10"/>
   </cols>
@@ -12110,7 +11670,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="I9" s="4" t="n">
@@ -12260,7 +11820,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="I12" s="4" t="n">
@@ -12310,7 +11870,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
@@ -12660,7 +12220,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -12960,7 +12520,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="I26" s="4" t="n">
@@ -13060,7 +12620,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
@@ -13310,7 +12870,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="I33" s="4" t="n">
@@ -13510,7 +13070,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="I37" s="4" t="n">
@@ -13760,7 +13320,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="I42" s="4" t="n">
@@ -13960,7 +13520,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="I46" s="4" t="n">
@@ -14060,7 +13620,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="I48" s="4" t="n">
@@ -14310,7 +13870,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="I53" s="4" t="n">
@@ -14577,7 +14137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14592,7 +14152,7 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -15211,7 +14771,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -15427,7 +14987,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -15499,7 +15059,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -16003,7 +15563,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -16435,7 +15995,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -16579,7 +16139,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -16939,7 +16499,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -17227,7 +16787,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -17587,7 +17147,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -17875,7 +17435,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -18019,7 +17579,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -18379,7 +17939,7 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -18783,7 +18343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18801,8 +18361,8 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -18853,12 +18413,12 @@
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>Pytest</t>
+          <t>Supertest / NodeRunner</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>Cypress</t>
+          <t>Jest (RNTL)</t>
         </is>
       </c>
     </row>
@@ -18902,12 +18462,8 @@
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
@@ -18944,17 +18500,13 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -18996,12 +18548,8 @@
       <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -19043,12 +18591,8 @@
       <c r="I5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -19090,12 +18634,8 @@
       <c r="I6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -19137,12 +18677,8 @@
       <c r="I7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -19179,17 +18715,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -19231,12 +18763,8 @@
       <c r="I9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -19278,12 +18806,8 @@
       <c r="I10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -19325,12 +18849,8 @@
       <c r="I11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -19372,12 +18892,8 @@
       <c r="I12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
@@ -19417,14 +18933,10 @@
         <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -19466,12 +18978,8 @@
       <c r="I14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
@@ -19513,12 +19021,8 @@
       <c r="I15" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -19560,12 +19064,8 @@
       <c r="I16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
@@ -19602,17 +19102,13 @@
         <v>3</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -19652,14 +19148,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -19701,12 +19193,8 @@
       <c r="I19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -19746,14 +19234,10 @@
         <v>0</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -19795,12 +19279,8 @@
       <c r="I21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
@@ -19842,12 +19322,8 @@
       <c r="I22" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
@@ -19887,14 +19363,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
@@ -19936,12 +19408,8 @@
       <c r="I24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
@@ -19981,14 +19449,10 @@
         <v>2</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
@@ -20030,12 +19494,8 @@
       <c r="I26" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
@@ -20075,14 +19535,10 @@
         <v>0</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
@@ -20124,12 +19580,8 @@
       <c r="I28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
@@ -20171,12 +19623,8 @@
       <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
@@ -20218,12 +19666,8 @@
       <c r="I30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
@@ -20265,11 +19709,205 @@
       <c r="I31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>0</v>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Definición y Criterio Establecido</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Alcance de Pruebas</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura derivada al 100% de la lista de Requisitos Funcionales (47) y No Funcionales (21) de EcoAlerta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Ambiente de Pruebas</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Backend Node.js v24 con TypeScript v5, base de datos de test SQLite/PostgreSQL aislada con Prisma ORM, cliente móvil React Native Expo SDK 52.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Convención de Rutas API</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Rutas REST bajo prefijo /api/: /auth/register, /auth/login, /denuncias, /productos, /canjes, /sucursales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Datos de Prueba Deterministas</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Uso de fixtures controlados y semillas predecibles (npm run prisma:seed) para garantizar reproducibilidad exacta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Política de Corrección de Bugs</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>El responsable exclusivo de analizar, depurar y corregir los defectos es el mismo desarrollador que implementó el módulo o función.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Gestión de Concurrencia</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Validación estricta de atomicidad mediante transacciones prisma.$transaction en toma 1 a 1 de casos y reserva de stock TTL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Política de Ecopuntos</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Los puntos solo se acreditan cuando el Administrador confirma la veracidad del foco ambiental en terreno. Nunca se otorgan en la creación inicial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Política de Expiración de Canjes</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Los pedidos no retirados tras 30 días corridos pasan a EXPIRADO; el stock vuelve al inventario y los puntos NO se reembolsan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Protocolo de Inaccesibilidad</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Se toleran hasta 3 visitas con aviso municipal pegado. Al 3.er intento fallido el caso se cierra como CERRADO_INACCESIBLE para derivación legal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Compresión Multimedia (RNF-02)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Toda fotografía debe procesarse en cliente reduciendo su peso obligatoriamente a &lt; 1.2 MB antes de cualquier transferencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Feedback Transaccional (RNF-10)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Toda mutación a base de datos despliega en el ms 0 el TransactionLoaderModal bloqueando toques repetidos del usuario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Criterios de Aceptación BDD</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Todos los criterios de aceptación se redactan y validan formalmente en sintaxis Gherkin (Dado / Cuando / Entonces).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Modelo de Calidad ISO 25010</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Adopción de ISO/IEC 25010 como marco de referencia metodológica y guía de buenas prácticas de calidad para mantener consistencia, sin pretensión de certificación externa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Respaldo de Evidencias y Packs de Datos</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Cada caso de prueba cuenta con su Request, Response y Pack de Datos exacto registrado en el Dossier de Evidencias (08_DOSSIER_EVIDENCIAS_DE_PRUEBA.md) y en la colección oficial exportada de Postman.</t>
+        </is>
       </c>
     </row>
   </sheetData>
